--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -518,9 +518,65 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B3" s="1">
+        <v>287</v>
+      </c>
+      <c r="C3" s="1">
+        <v>198</v>
+      </c>
+      <c r="D3" s="1">
+        <v>40</v>
+      </c>
+      <c r="E3" s="1">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L3" s="1">
+        <v>40</v>
+      </c>
+      <c r="M3" s="1">
+        <v>10</v>
+      </c>
+      <c r="N3" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O3" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P3" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="R3" s="1" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -529,23 +529,23 @@
         <v>198</v>
       </c>
       <c r="D3" s="1">
+        <v>60</v>
+      </c>
+      <c r="E3" s="1">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1">
+        <v>60</v>
+      </c>
+      <c r="G3" s="1">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1">
         <v>40</v>
       </c>
-      <c r="E3" s="1">
+      <c r="I3" s="1">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="H3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I3" s="1" t="str">
-        <v/>
-      </c>
       <c r="J3" s="1" t="str">
         <v/>
       </c>
@@ -553,10 +553,10 @@
         <v/>
       </c>
       <c r="L3" s="1">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="M3" s="1">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -484,11 +484,11 @@
       <c r="G2" s="1" t="str">
         <v/>
       </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="H2" s="1">
+        <v>60</v>
+      </c>
+      <c r="I2" s="1">
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -497,10 +497,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="M2" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -478,11 +478,11 @@
       <c r="E2" s="1">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
       </c>
       <c r="H2" s="1">
         <v>60</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -453,74 +453,80 @@
         <v>meds_taken</v>
       </c>
       <c r="P1" s="1" t="str">
+        <v>water_72oz</v>
+      </c>
+      <c r="Q1" s="1" t="str">
         <v>exercised</v>
       </c>
-      <c r="Q1" s="1" t="str">
+      <c r="R1" s="1" t="str">
         <v>exercise_notes</v>
       </c>
-      <c r="R1" s="1" t="str">
+      <c r="S1" s="1" t="str">
         <v>notes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="B2" s="1">
-        <v>287</v>
+        <v>2026-05-04</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v/>
       </c>
       <c r="C2" s="1">
-        <v>198</v>
-      </c>
-      <c r="D2" s="1">
-        <v>40</v>
-      </c>
-      <c r="E2" s="1">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1">
+        <v>172</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1">
+      <c r="M2" s="1">
         <v>0</v>
       </c>
-      <c r="H2" s="1">
-        <v>60</v>
-      </c>
-      <c r="I2" s="1">
-        <v>20</v>
-      </c>
-      <c r="J2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L2" s="1">
-        <v>100</v>
-      </c>
-      <c r="M2" s="1">
-        <v>30</v>
-      </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="Q2" s="1" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="R2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S2" s="1" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B3" s="1">
         <v>287</v>
@@ -529,22 +535,22 @@
         <v>198</v>
       </c>
       <c r="D3" s="1">
+        <v>40</v>
+      </c>
+      <c r="E3" s="1">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
         <v>60</v>
       </c>
-      <c r="E3" s="1">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1">
-        <v>60</v>
-      </c>
-      <c r="G3" s="1">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1">
-        <v>40</v>
-      </c>
       <c r="I3" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J3" s="1" t="str">
         <v/>
@@ -553,10 +559,10 @@
         <v/>
       </c>
       <c r="L3" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M3" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -568,15 +574,77 @@
         <v>no</v>
       </c>
       <c r="Q3" s="1" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="R3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S3" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B4" s="1">
+        <v>287</v>
+      </c>
+      <c r="C4" s="1">
+        <v>198</v>
+      </c>
+      <c r="D4" s="1">
+        <v>60</v>
+      </c>
+      <c r="E4" s="1">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1">
+        <v>60</v>
+      </c>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1">
+        <v>40</v>
+      </c>
+      <c r="I4" s="1">
+        <v>10</v>
+      </c>
+      <c r="J4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L4" s="1">
+        <v>160</v>
+      </c>
+      <c r="M4" s="1">
+        <v>35</v>
+      </c>
+      <c r="N4" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O4" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P4" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q4" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S4" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -475,11 +475,11 @@
       <c r="C2" s="1">
         <v>172</v>
       </c>
-      <c r="D2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
-        <v/>
+      <c r="D2" s="1">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -469,8 +469,8 @@
       <c r="A2" s="1" t="str">
         <v>2026-05-04</v>
       </c>
-      <c r="B2" s="1" t="str">
-        <v/>
+      <c r="B2" s="1">
+        <v>291</v>
       </c>
       <c r="C2" s="1">
         <v>172</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -481,11 +481,11 @@
       <c r="E2" s="1">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
+      <c r="F2" s="1">
+        <v>40</v>
+      </c>
+      <c r="G2" s="1">
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="M2" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -487,11 +487,11 @@
       <c r="G2" s="1">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="H2" s="1">
+        <v>40</v>
+      </c>
+      <c r="I2" s="1">
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="M2" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -493,17 +493,17 @@
       <c r="I2" s="1">
         <v>20</v>
       </c>
-      <c r="J2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K2" s="1" t="str">
-        <v/>
+      <c r="J2" s="1">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1">
+        <v>2</v>
       </c>
       <c r="L2" s="1">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="M2" s="1">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,49 +467,49 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B2" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C2" s="1">
-        <v>172</v>
-      </c>
-      <c r="D2" s="1">
-        <v>30</v>
-      </c>
-      <c r="E2" s="1">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1">
-        <v>40</v>
-      </c>
-      <c r="G2" s="1">
-        <v>15</v>
-      </c>
-      <c r="H2" s="1">
-        <v>40</v>
-      </c>
-      <c r="I2" s="1">
-        <v>20</v>
-      </c>
-      <c r="J2" s="1">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1">
-        <v>2</v>
+        <v>223</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K2" s="1" t="str">
+        <v/>
       </c>
       <c r="L2" s="1">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>
@@ -526,43 +526,43 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B3" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C3" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D3" s="1">
+        <v>30</v>
+      </c>
+      <c r="E3" s="1">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1">
         <v>40</v>
       </c>
-      <c r="E3" s="1">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I3" s="1">
         <v>20</v>
       </c>
-      <c r="J3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K3" s="1" t="str">
-        <v/>
+      <c r="J3" s="1">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1">
+        <v>2</v>
       </c>
       <c r="L3" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M3" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B4" s="1">
         <v>287</v>
@@ -594,22 +594,22 @@
         <v>198</v>
       </c>
       <c r="D4" s="1">
+        <v>40</v>
+      </c>
+      <c r="E4" s="1">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
         <v>60</v>
       </c>
-      <c r="E4" s="1">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1">
-        <v>60</v>
-      </c>
-      <c r="G4" s="1">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1">
-        <v>40</v>
-      </c>
       <c r="I4" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J4" s="1" t="str">
         <v/>
@@ -618,10 +618,10 @@
         <v/>
       </c>
       <c r="L4" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M4" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -639,12 +639,71 @@
         <v/>
       </c>
       <c r="S4" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B5" s="1">
+        <v>287</v>
+      </c>
+      <c r="C5" s="1">
+        <v>198</v>
+      </c>
+      <c r="D5" s="1">
+        <v>60</v>
+      </c>
+      <c r="E5" s="1">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1">
+        <v>60</v>
+      </c>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>40</v>
+      </c>
+      <c r="I5" s="1">
+        <v>10</v>
+      </c>
+      <c r="J5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L5" s="1">
+        <v>160</v>
+      </c>
+      <c r="M5" s="1">
+        <v>35</v>
+      </c>
+      <c r="N5" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O5" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P5" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q5" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S5" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -475,17 +475,17 @@
       <c r="C2" s="1">
         <v>223</v>
       </c>
-      <c r="D2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
+      <c r="D2" s="1">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>60</v>
+      </c>
+      <c r="G2" s="1">
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -487,11 +487,11 @@
       <c r="G2" s="1">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="H2" s="1">
+        <v>60</v>
+      </c>
+      <c r="I2" s="1">
+        <v>15</v>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="M2" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S6"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,49 +467,49 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-05</v>
-      </c>
-      <c r="B2" s="1">
-        <v>286</v>
+        <v>2026-05-06</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v/>
       </c>
       <c r="C2" s="1">
-        <v>223</v>
-      </c>
-      <c r="D2" s="1">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1">
+        <v>302</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" s="1">
-        <v>60</v>
-      </c>
-      <c r="G2" s="1">
-        <v>15</v>
-      </c>
-      <c r="H2" s="1">
-        <v>60</v>
-      </c>
-      <c r="I2" s="1">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L2" s="1">
-        <v>128</v>
-      </c>
       <c r="M2" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>
@@ -526,43 +526,43 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B3" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C3" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D3" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G3" s="1">
         <v>15</v>
       </c>
       <c r="H3" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I3" s="1">
-        <v>20</v>
-      </c>
-      <c r="J3" s="1">
-        <v>20</v>
-      </c>
-      <c r="K3" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K3" s="1" t="str">
+        <v/>
       </c>
       <c r="L3" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M3" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -585,43 +585,43 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B4" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C4" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D4" s="1">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1">
         <v>40</v>
       </c>
-      <c r="E4" s="1">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1">
         <v>20</v>
       </c>
-      <c r="J4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K4" s="1" t="str">
-        <v/>
+      <c r="J4" s="1">
+        <v>20</v>
+      </c>
+      <c r="K4" s="1">
+        <v>2</v>
       </c>
       <c r="L4" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M4" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -644,7 +644,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B5" s="1">
         <v>287</v>
@@ -653,22 +653,22 @@
         <v>198</v>
       </c>
       <c r="D5" s="1">
+        <v>40</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
         <v>60</v>
       </c>
-      <c r="E5" s="1">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1">
-        <v>60</v>
-      </c>
-      <c r="G5" s="1">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
-        <v>40</v>
-      </c>
       <c r="I5" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J5" s="1" t="str">
         <v/>
@@ -677,10 +677,10 @@
         <v/>
       </c>
       <c r="L5" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M5" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -698,12 +698,71 @@
         <v/>
       </c>
       <c r="S5" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B6" s="1">
+        <v>287</v>
+      </c>
+      <c r="C6" s="1">
+        <v>198</v>
+      </c>
+      <c r="D6" s="1">
+        <v>60</v>
+      </c>
+      <c r="E6" s="1">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1">
+        <v>60</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>40</v>
+      </c>
+      <c r="I6" s="1">
+        <v>10</v>
+      </c>
+      <c r="J6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L6" s="1">
+        <v>160</v>
+      </c>
+      <c r="M6" s="1">
+        <v>35</v>
+      </c>
+      <c r="N6" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O6" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P6" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q6" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S6" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -469,23 +469,23 @@
       <c r="A2" s="1" t="str">
         <v>2026-05-06</v>
       </c>
-      <c r="B2" s="1" t="str">
-        <v/>
+      <c r="B2" s="1">
+        <v>257</v>
       </c>
       <c r="C2" s="1">
         <v>302</v>
       </c>
-      <c r="D2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
+      <c r="D2" s="1">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>40</v>
+      </c>
+      <c r="G2" s="1">
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -487,11 +487,11 @@
       <c r="G2" s="1">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>80</v>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -503,7 +503,7 @@
         <v>48</v>
       </c>
       <c r="M2" s="1">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -521,7 +521,7 @@
         <v/>
       </c>
       <c r="S2" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="3">

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -493,17 +493,17 @@
       <c r="I2" s="1">
         <v>80</v>
       </c>
-      <c r="J2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K2" s="1" t="str">
-        <v/>
+      <c r="J2" s="1">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1">
+        <v>5</v>
       </c>
       <c r="L2" s="1">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="M2" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -497,13 +497,13 @@
         <v>30</v>
       </c>
       <c r="K2" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L2" s="1">
         <v>78</v>
       </c>
       <c r="M2" s="1">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -497,13 +497,13 @@
         <v>30</v>
       </c>
       <c r="K2" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L2" s="1">
         <v>78</v>
       </c>
       <c r="M2" s="1">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S7"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,43 +467,43 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="B2" s="1">
-        <v>257</v>
+        <v>2026-05-07</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v/>
       </c>
       <c r="C2" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D2" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
-        <v>40</v>
-      </c>
-      <c r="G2" s="1">
-        <v>15</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1">
-        <v>80</v>
-      </c>
-      <c r="J2" s="1">
-        <v>30</v>
-      </c>
-      <c r="K2" s="1">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K2" s="1" t="str">
+        <v/>
       </c>
       <c r="L2" s="1">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="M2" s="1">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
@@ -521,18 +521,18 @@
         <v/>
       </c>
       <c r="S2" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B3" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C3" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D3" s="1">
         <v>8</v>
@@ -541,28 +541,28 @@
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G3" s="1">
         <v>15</v>
       </c>
       <c r="H3" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>15</v>
-      </c>
-      <c r="J3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K3" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J3" s="1">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1">
+        <v>5</v>
       </c>
       <c r="L3" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M3" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -580,48 +580,48 @@
         <v/>
       </c>
       <c r="S3" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B4" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C4" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D4" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G4" s="1">
         <v>15</v>
       </c>
       <c r="H4" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I4" s="1">
-        <v>20</v>
-      </c>
-      <c r="J4" s="1">
-        <v>20</v>
-      </c>
-      <c r="K4" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K4" s="1" t="str">
+        <v/>
       </c>
       <c r="L4" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M4" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -644,43 +644,43 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B5" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C5" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D5" s="1">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1">
         <v>40</v>
       </c>
-      <c r="E5" s="1">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H5" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I5" s="1">
         <v>20</v>
       </c>
-      <c r="J5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K5" s="1" t="str">
-        <v/>
+      <c r="J5" s="1">
+        <v>20</v>
+      </c>
+      <c r="K5" s="1">
+        <v>2</v>
       </c>
       <c r="L5" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M5" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -703,7 +703,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B6" s="1">
         <v>287</v>
@@ -712,22 +712,22 @@
         <v>198</v>
       </c>
       <c r="D6" s="1">
+        <v>40</v>
+      </c>
+      <c r="E6" s="1">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>60</v>
       </c>
-      <c r="E6" s="1">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1">
-        <v>60</v>
-      </c>
-      <c r="G6" s="1">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <v>40</v>
-      </c>
       <c r="I6" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J6" s="1" t="str">
         <v/>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="L6" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M6" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -757,12 +757,71 @@
         <v/>
       </c>
       <c r="S6" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B7" s="1">
+        <v>287</v>
+      </c>
+      <c r="C7" s="1">
+        <v>198</v>
+      </c>
+      <c r="D7" s="1">
+        <v>60</v>
+      </c>
+      <c r="E7" s="1">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1">
+        <v>60</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1">
+        <v>40</v>
+      </c>
+      <c r="I7" s="1">
+        <v>10</v>
+      </c>
+      <c r="J7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L7" s="1">
+        <v>160</v>
+      </c>
+      <c r="M7" s="1">
+        <v>35</v>
+      </c>
+      <c r="N7" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O7" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P7" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q7" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S7" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S8"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,19 +467,19 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B2" s="1" t="str">
         <v/>
       </c>
       <c r="C2" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D2" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="M2" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
@@ -526,43 +526,43 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-06</v>
-      </c>
-      <c r="B3" s="1">
-        <v>257</v>
+        <v>2026-05-07</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <v/>
       </c>
       <c r="C3" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D3" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
-        <v>40</v>
-      </c>
-      <c r="G3" s="1">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1">
-        <v>80</v>
-      </c>
-      <c r="J3" s="1">
-        <v>30</v>
-      </c>
-      <c r="K3" s="1">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K3" s="1" t="str">
+        <v/>
       </c>
       <c r="L3" s="1">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="M3" s="1">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -580,18 +580,18 @@
         <v/>
       </c>
       <c r="S3" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B4" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C4" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D4" s="1">
         <v>8</v>
@@ -600,28 +600,28 @@
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G4" s="1">
         <v>15</v>
       </c>
       <c r="H4" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>15</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K4" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J4" s="1">
+        <v>30</v>
+      </c>
+      <c r="K4" s="1">
+        <v>5</v>
       </c>
       <c r="L4" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M4" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -639,48 +639,48 @@
         <v/>
       </c>
       <c r="S4" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B5" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C5" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D5" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G5" s="1">
         <v>15</v>
       </c>
       <c r="H5" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I5" s="1">
-        <v>20</v>
-      </c>
-      <c r="J5" s="1">
-        <v>20</v>
-      </c>
-      <c r="K5" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K5" s="1" t="str">
+        <v/>
       </c>
       <c r="L5" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M5" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -703,43 +703,43 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B6" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C6" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D6" s="1">
+        <v>30</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1">
         <v>40</v>
       </c>
-      <c r="E6" s="1">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H6" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I6" s="1">
         <v>20</v>
       </c>
-      <c r="J6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K6" s="1" t="str">
-        <v/>
+      <c r="J6" s="1">
+        <v>20</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2</v>
       </c>
       <c r="L6" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M6" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B7" s="1">
         <v>287</v>
@@ -771,22 +771,22 @@
         <v>198</v>
       </c>
       <c r="D7" s="1">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>60</v>
       </c>
-      <c r="E7" s="1">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1">
-        <v>60</v>
-      </c>
-      <c r="G7" s="1">
-        <v>10</v>
-      </c>
-      <c r="H7" s="1">
-        <v>40</v>
-      </c>
       <c r="I7" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J7" s="1" t="str">
         <v/>
@@ -795,10 +795,10 @@
         <v/>
       </c>
       <c r="L7" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M7" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -816,12 +816,71 @@
         <v/>
       </c>
       <c r="S7" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B8" s="1">
+        <v>287</v>
+      </c>
+      <c r="C8" s="1">
+        <v>198</v>
+      </c>
+      <c r="D8" s="1">
+        <v>60</v>
+      </c>
+      <c r="E8" s="1">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1">
+        <v>60</v>
+      </c>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>40</v>
+      </c>
+      <c r="I8" s="1">
+        <v>10</v>
+      </c>
+      <c r="J8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L8" s="1">
+        <v>160</v>
+      </c>
+      <c r="M8" s="1">
+        <v>35</v>
+      </c>
+      <c r="N8" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O8" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P8" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q8" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S8" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -540,17 +540,17 @@
       <c r="E3" s="1">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="H3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I3" s="1" t="str">
-        <v/>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1">
+        <v>40</v>
+      </c>
+      <c r="I3" s="1">
+        <v>15</v>
       </c>
       <c r="J3" s="1" t="str">
         <v/>
@@ -559,10 +559,10 @@
         <v/>
       </c>
       <c r="L3" s="1">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="M3" s="1">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -528,8 +528,8 @@
       <c r="A3" s="1" t="str">
         <v>2026-05-07</v>
       </c>
-      <c r="B3" s="1" t="str">
-        <v/>
+      <c r="B3" s="1">
+        <v>283</v>
       </c>
       <c r="C3" s="1">
         <v>233</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -469,8 +469,8 @@
       <c r="A2" s="1" t="str">
         <v>2026-05-08</v>
       </c>
-      <c r="B2" s="1" t="str">
-        <v/>
+      <c r="B2" s="1">
+        <v>286</v>
       </c>
       <c r="C2" s="1">
         <v>188</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -481,17 +481,17 @@
       <c r="E2" s="1">
         <v>20</v>
       </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="F2" s="1">
+        <v>45</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1">
+        <v>50</v>
+      </c>
+      <c r="I2" s="1">
+        <v>10</v>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="M2" s="1">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,31 +467,31 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B2" s="1">
-        <v>286</v>
-      </c>
-      <c r="C2" s="1">
-        <v>188</v>
+        <v>285</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v/>
       </c>
       <c r="D2" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E2" s="1">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1">
-        <v>45</v>
-      </c>
-      <c r="G2" s="1">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1">
-        <v>50</v>
-      </c>
-      <c r="I2" s="1">
-        <v>10</v>
+        <v>80</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v/>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="M2" s="1">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>
@@ -526,32 +526,32 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B3" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C3" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D3" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G3" s="1">
+        <v>5</v>
+      </c>
+      <c r="H3" s="1">
+        <v>50</v>
+      </c>
+      <c r="I3" s="1">
         <v>10</v>
       </c>
-      <c r="H3" s="1">
-        <v>40</v>
-      </c>
-      <c r="I3" s="1">
-        <v>15</v>
-      </c>
       <c r="J3" s="1" t="str">
         <v/>
       </c>
@@ -559,10 +559,10 @@
         <v/>
       </c>
       <c r="L3" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M3" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -585,43 +585,43 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B4" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C4" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E4" s="1">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1">
         <v>40</v>
       </c>
-      <c r="G4" s="1">
+      <c r="I4" s="1">
         <v>15</v>
       </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>80</v>
-      </c>
-      <c r="J4" s="1">
-        <v>30</v>
-      </c>
-      <c r="K4" s="1">
-        <v>5</v>
+      <c r="J4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K4" s="1" t="str">
+        <v/>
       </c>
       <c r="L4" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M4" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -639,18 +639,18 @@
         <v/>
       </c>
       <c r="S4" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B5" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C5" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D5" s="1">
         <v>8</v>
@@ -659,28 +659,28 @@
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G5" s="1">
         <v>15</v>
       </c>
       <c r="H5" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>15</v>
-      </c>
-      <c r="J5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K5" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J5" s="1">
+        <v>30</v>
+      </c>
+      <c r="K5" s="1">
+        <v>5</v>
       </c>
       <c r="L5" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M5" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -698,48 +698,48 @@
         <v/>
       </c>
       <c r="S5" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B6" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C6" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D6" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G6" s="1">
         <v>15</v>
       </c>
       <c r="H6" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I6" s="1">
-        <v>20</v>
-      </c>
-      <c r="J6" s="1">
-        <v>20</v>
-      </c>
-      <c r="K6" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K6" s="1" t="str">
+        <v/>
       </c>
       <c r="L6" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M6" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -762,43 +762,43 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B7" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C7" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D7" s="1">
+        <v>30</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1">
         <v>40</v>
       </c>
-      <c r="E7" s="1">
-        <v>10</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H7" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I7" s="1">
         <v>20</v>
       </c>
-      <c r="J7" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K7" s="1" t="str">
-        <v/>
+      <c r="J7" s="1">
+        <v>20</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2</v>
       </c>
       <c r="L7" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M7" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -821,7 +821,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B8" s="1">
         <v>287</v>
@@ -830,22 +830,22 @@
         <v>198</v>
       </c>
       <c r="D8" s="1">
+        <v>40</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>60</v>
       </c>
-      <c r="E8" s="1">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1">
-        <v>60</v>
-      </c>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>40</v>
-      </c>
       <c r="I8" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J8" s="1" t="str">
         <v/>
@@ -854,10 +854,10 @@
         <v/>
       </c>
       <c r="L8" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M8" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N8" s="1" t="str">
         <v>no</v>
@@ -875,12 +875,71 @@
         <v/>
       </c>
       <c r="S8" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B9" s="1">
+        <v>287</v>
+      </c>
+      <c r="C9" s="1">
+        <v>198</v>
+      </c>
+      <c r="D9" s="1">
+        <v>60</v>
+      </c>
+      <c r="E9" s="1">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1">
+        <v>60</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>40</v>
+      </c>
+      <c r="I9" s="1">
+        <v>10</v>
+      </c>
+      <c r="J9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L9" s="1">
+        <v>160</v>
+      </c>
+      <c r="M9" s="1">
+        <v>35</v>
+      </c>
+      <c r="N9" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O9" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P9" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q9" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S9" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -472,8 +472,8 @@
       <c r="B2" s="1">
         <v>285</v>
       </c>
-      <c r="C2" s="1" t="str">
-        <v/>
+      <c r="C2" s="1">
+        <v>256</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -481,11 +481,11 @@
       <c r="E2" s="1">
         <v>80</v>
       </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
+      <c r="F2" s="1">
+        <v>40</v>
+      </c>
+      <c r="G2" s="1">
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="M2" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -493,23 +493,23 @@
       <c r="I2" s="1" t="str">
         <v/>
       </c>
-      <c r="J2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K2" s="1" t="str">
-        <v/>
+      <c r="J2" s="1">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1">
+        <v>10</v>
       </c>
       <c r="L2" s="1">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="M2" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>
@@ -521,7 +521,7 @@
         <v/>
       </c>
       <c r="S2" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="3">

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -487,11 +487,11 @@
       <c r="G2" s="1">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="H2" s="1">
+        <v>60</v>
+      </c>
+      <c r="I2" s="1">
+        <v>20</v>
       </c>
       <c r="J2" s="1">
         <v>20</v>
@@ -500,10 +500,10 @@
         <v>10</v>
       </c>
       <c r="L2" s="1">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="M2" s="1">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
@@ -512,7 +512,7 @@
         <v>yes</v>
       </c>
       <c r="P2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S10"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,52 +467,52 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B2" s="1">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C2" s="1">
-        <v>256</v>
-      </c>
-      <c r="D2" s="1">
-        <v>30</v>
-      </c>
-      <c r="E2" s="1">
-        <v>80</v>
-      </c>
-      <c r="F2" s="1">
-        <v>40</v>
-      </c>
-      <c r="G2" s="1">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1">
-        <v>60</v>
-      </c>
-      <c r="I2" s="1">
-        <v>20</v>
-      </c>
-      <c r="J2" s="1">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1">
-        <v>10</v>
+        <v>155</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K2" s="1" t="str">
+        <v/>
       </c>
       <c r="L2" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="Q2" s="1" t="str">
         <v>no</v>
@@ -521,48 +521,48 @@
         <v/>
       </c>
       <c r="S2" s="1" t="str">
-        <v>Sugar dip snack</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B3" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C3" s="1">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D3" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1">
+        <v>80</v>
+      </c>
+      <c r="F3" s="1">
+        <v>40</v>
+      </c>
+      <c r="G3" s="1">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1">
+        <v>60</v>
+      </c>
+      <c r="I3" s="1">
         <v>20</v>
       </c>
-      <c r="F3" s="1">
-        <v>45</v>
-      </c>
-      <c r="G3" s="1">
-        <v>5</v>
-      </c>
-      <c r="H3" s="1">
-        <v>50</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1">
         <v>10</v>
       </c>
-      <c r="J3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K3" s="1" t="str">
-        <v/>
-      </c>
       <c r="L3" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M3" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -571,7 +571,7 @@
         <v>yes</v>
       </c>
       <c r="P3" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q3" s="1" t="str">
         <v>no</v>
@@ -580,37 +580,37 @@
         <v/>
       </c>
       <c r="S3" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B4" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C4" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D4" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G4" s="1">
+        <v>5</v>
+      </c>
+      <c r="H4" s="1">
+        <v>50</v>
+      </c>
+      <c r="I4" s="1">
         <v>10</v>
       </c>
-      <c r="H4" s="1">
-        <v>40</v>
-      </c>
-      <c r="I4" s="1">
-        <v>15</v>
-      </c>
       <c r="J4" s="1" t="str">
         <v/>
       </c>
@@ -618,10 +618,10 @@
         <v/>
       </c>
       <c r="L4" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M4" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -644,43 +644,43 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B5" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C5" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D5" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E5" s="1">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
         <v>40</v>
       </c>
-      <c r="G5" s="1">
+      <c r="I5" s="1">
         <v>15</v>
       </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>80</v>
-      </c>
-      <c r="J5" s="1">
-        <v>30</v>
-      </c>
-      <c r="K5" s="1">
-        <v>5</v>
+      <c r="J5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K5" s="1" t="str">
+        <v/>
       </c>
       <c r="L5" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M5" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -698,18 +698,18 @@
         <v/>
       </c>
       <c r="S5" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B6" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C6" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D6" s="1">
         <v>8</v>
@@ -718,28 +718,28 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
         <v>15</v>
       </c>
       <c r="H6" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>15</v>
-      </c>
-      <c r="J6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K6" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J6" s="1">
+        <v>30</v>
+      </c>
+      <c r="K6" s="1">
+        <v>5</v>
       </c>
       <c r="L6" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M6" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -757,48 +757,48 @@
         <v/>
       </c>
       <c r="S6" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B7" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C7" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D7" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1">
         <v>15</v>
       </c>
       <c r="H7" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I7" s="1">
-        <v>20</v>
-      </c>
-      <c r="J7" s="1">
-        <v>20</v>
-      </c>
-      <c r="K7" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K7" s="1" t="str">
+        <v/>
       </c>
       <c r="L7" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M7" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -821,43 +821,43 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B8" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C8" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D8" s="1">
+        <v>30</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1">
         <v>40</v>
       </c>
-      <c r="E8" s="1">
-        <v>10</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H8" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I8" s="1">
         <v>20</v>
       </c>
-      <c r="J8" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K8" s="1" t="str">
-        <v/>
+      <c r="J8" s="1">
+        <v>20</v>
+      </c>
+      <c r="K8" s="1">
+        <v>2</v>
       </c>
       <c r="L8" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M8" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N8" s="1" t="str">
         <v>no</v>
@@ -880,7 +880,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B9" s="1">
         <v>287</v>
@@ -889,22 +889,22 @@
         <v>198</v>
       </c>
       <c r="D9" s="1">
+        <v>40</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>60</v>
       </c>
-      <c r="E9" s="1">
-        <v>15</v>
-      </c>
-      <c r="F9" s="1">
-        <v>60</v>
-      </c>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>40</v>
-      </c>
       <c r="I9" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J9" s="1" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v/>
       </c>
       <c r="L9" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M9" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N9" s="1" t="str">
         <v>no</v>
@@ -934,12 +934,71 @@
         <v/>
       </c>
       <c r="S9" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B10" s="1">
+        <v>287</v>
+      </c>
+      <c r="C10" s="1">
+        <v>198</v>
+      </c>
+      <c r="D10" s="1">
+        <v>60</v>
+      </c>
+      <c r="E10" s="1">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1">
+        <v>60</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>40</v>
+      </c>
+      <c r="I10" s="1">
+        <v>10</v>
+      </c>
+      <c r="J10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L10" s="1">
+        <v>160</v>
+      </c>
+      <c r="M10" s="1">
+        <v>35</v>
+      </c>
+      <c r="N10" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O10" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P10" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q10" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S10" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -475,11 +475,11 @@
       <c r="C2" s="1">
         <v>155</v>
       </c>
-      <c r="D2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
-        <v/>
+      <c r="D2" s="1">
+        <v>60</v>
+      </c>
+      <c r="E2" s="1">
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -481,11 +481,11 @@
       <c r="E2" s="1">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
+      <c r="F2" s="1">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1">
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="M2" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,26 +467,26 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="B2" s="1">
-        <v>282</v>
-      </c>
-      <c r="C2" s="1">
-        <v>155</v>
+        <v>2026-05-11</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v/>
       </c>
       <c r="D2" s="1">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1">
         <v>15</v>
       </c>
-      <c r="F2" s="1">
-        <v>30</v>
-      </c>
-      <c r="G2" s="1">
-        <v>10</v>
-      </c>
       <c r="H2" s="1" t="str">
         <v/>
       </c>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="M2" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
@@ -526,43 +526,43 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B3" s="1">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C3" s="1">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="D3" s="1">
+        <v>60</v>
+      </c>
+      <c r="E3" s="1">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1">
         <v>30</v>
-      </c>
-      <c r="E3" s="1">
-        <v>80</v>
-      </c>
-      <c r="F3" s="1">
-        <v>40</v>
       </c>
       <c r="G3" s="1">
         <v>10</v>
       </c>
-      <c r="H3" s="1">
-        <v>60</v>
-      </c>
-      <c r="I3" s="1">
-        <v>20</v>
-      </c>
-      <c r="J3" s="1">
-        <v>20</v>
-      </c>
-      <c r="K3" s="1">
-        <v>10</v>
+      <c r="H3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K3" s="1" t="str">
+        <v/>
       </c>
       <c r="L3" s="1">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M3" s="1">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -571,7 +571,7 @@
         <v>yes</v>
       </c>
       <c r="P3" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="Q3" s="1" t="str">
         <v>no</v>
@@ -580,48 +580,48 @@
         <v/>
       </c>
       <c r="S3" s="1" t="str">
-        <v>Sugar dip snack</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B4" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C4" s="1">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D4" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E4" s="1">
+        <v>80</v>
+      </c>
+      <c r="F4" s="1">
+        <v>40</v>
+      </c>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1">
+        <v>60</v>
+      </c>
+      <c r="I4" s="1">
         <v>20</v>
       </c>
-      <c r="F4" s="1">
-        <v>45</v>
-      </c>
-      <c r="G4" s="1">
-        <v>5</v>
-      </c>
-      <c r="H4" s="1">
-        <v>50</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
+        <v>20</v>
+      </c>
+      <c r="K4" s="1">
         <v>10</v>
       </c>
-      <c r="J4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K4" s="1" t="str">
-        <v/>
-      </c>
       <c r="L4" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M4" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -630,7 +630,7 @@
         <v>yes</v>
       </c>
       <c r="P4" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q4" s="1" t="str">
         <v>no</v>
@@ -639,37 +639,37 @@
         <v/>
       </c>
       <c r="S4" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B5" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C5" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D5" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G5" s="1">
+        <v>5</v>
+      </c>
+      <c r="H5" s="1">
+        <v>50</v>
+      </c>
+      <c r="I5" s="1">
         <v>10</v>
       </c>
-      <c r="H5" s="1">
-        <v>40</v>
-      </c>
-      <c r="I5" s="1">
-        <v>15</v>
-      </c>
       <c r="J5" s="1" t="str">
         <v/>
       </c>
@@ -677,10 +677,10 @@
         <v/>
       </c>
       <c r="L5" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M5" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -703,43 +703,43 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B6" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C6" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D6" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E6" s="1">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1">
         <v>0</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
         <v>40</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>15</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>80</v>
-      </c>
-      <c r="J6" s="1">
-        <v>30</v>
-      </c>
-      <c r="K6" s="1">
-        <v>5</v>
+      <c r="J6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K6" s="1" t="str">
+        <v/>
       </c>
       <c r="L6" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M6" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -757,18 +757,18 @@
         <v/>
       </c>
       <c r="S6" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B7" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C7" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D7" s="1">
         <v>8</v>
@@ -777,28 +777,28 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
         <v>15</v>
       </c>
       <c r="H7" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>15</v>
-      </c>
-      <c r="J7" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K7" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J7" s="1">
+        <v>30</v>
+      </c>
+      <c r="K7" s="1">
+        <v>5</v>
       </c>
       <c r="L7" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M7" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -816,48 +816,48 @@
         <v/>
       </c>
       <c r="S7" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B8" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C8" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D8" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G8" s="1">
         <v>15</v>
       </c>
       <c r="H8" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I8" s="1">
-        <v>20</v>
-      </c>
-      <c r="J8" s="1">
-        <v>20</v>
-      </c>
-      <c r="K8" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K8" s="1" t="str">
+        <v/>
       </c>
       <c r="L8" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M8" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N8" s="1" t="str">
         <v>no</v>
@@ -880,43 +880,43 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B9" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C9" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D9" s="1">
+        <v>30</v>
+      </c>
+      <c r="E9" s="1">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1">
         <v>40</v>
       </c>
-      <c r="E9" s="1">
-        <v>10</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H9" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I9" s="1">
         <v>20</v>
       </c>
-      <c r="J9" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K9" s="1" t="str">
-        <v/>
+      <c r="J9" s="1">
+        <v>20</v>
+      </c>
+      <c r="K9" s="1">
+        <v>2</v>
       </c>
       <c r="L9" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M9" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N9" s="1" t="str">
         <v>no</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B10" s="1">
         <v>287</v>
@@ -948,22 +948,22 @@
         <v>198</v>
       </c>
       <c r="D10" s="1">
+        <v>40</v>
+      </c>
+      <c r="E10" s="1">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>60</v>
       </c>
-      <c r="E10" s="1">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1">
-        <v>60</v>
-      </c>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1">
-        <v>40</v>
-      </c>
       <c r="I10" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J10" s="1" t="str">
         <v/>
@@ -972,10 +972,10 @@
         <v/>
       </c>
       <c r="L10" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M10" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N10" s="1" t="str">
         <v>no</v>
@@ -993,12 +993,71 @@
         <v/>
       </c>
       <c r="S10" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B11" s="1">
+        <v>287</v>
+      </c>
+      <c r="C11" s="1">
+        <v>198</v>
+      </c>
+      <c r="D11" s="1">
+        <v>60</v>
+      </c>
+      <c r="E11" s="1">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1">
+        <v>60</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>40</v>
+      </c>
+      <c r="I11" s="1">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K11" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L11" s="1">
+        <v>160</v>
+      </c>
+      <c r="M11" s="1">
+        <v>35</v>
+      </c>
+      <c r="N11" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O11" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P11" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q11" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R11" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S11" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -485,7 +485,7 @@
         <v>50</v>
       </c>
       <c r="G2" s="1">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
@@ -503,7 +503,7 @@
         <v>65</v>
       </c>
       <c r="M2" s="1">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -487,11 +487,11 @@
       <c r="G2" s="1">
         <v>40</v>
       </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="H2" s="1">
+        <v>30</v>
+      </c>
+      <c r="I2" s="1">
+        <v>10</v>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="M2" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -472,8 +472,8 @@
       <c r="B2" s="1" t="str">
         <v/>
       </c>
-      <c r="C2" s="1" t="str">
-        <v/>
+      <c r="C2" s="1">
+        <v>232</v>
       </c>
       <c r="D2" s="1">
         <v>15</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S12"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,13 +467,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="B2" s="1" t="str">
         <v/>
       </c>
-      <c r="C2" s="1">
-        <v>232</v>
+      <c r="C2" s="1" t="str">
+        <v/>
       </c>
       <c r="D2" s="1">
         <v>15</v>
@@ -482,17 +482,17 @@
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1">
-        <v>40</v>
-      </c>
-      <c r="H2" s="1">
-        <v>30</v>
-      </c>
-      <c r="I2" s="1">
         <v>10</v>
       </c>
+      <c r="H2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v/>
+      </c>
       <c r="J2" s="1" t="str">
         <v/>
       </c>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="M2" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
@@ -526,32 +526,32 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="B3" s="1">
-        <v>282</v>
+        <v>2026-05-11</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <v/>
       </c>
       <c r="C3" s="1">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
+        <v>50</v>
+      </c>
+      <c r="G3" s="1">
+        <v>40</v>
+      </c>
+      <c r="H3" s="1">
         <v>30</v>
       </c>
-      <c r="G3" s="1">
+      <c r="I3" s="1">
         <v>10</v>
       </c>
-      <c r="H3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I3" s="1" t="str">
-        <v/>
-      </c>
       <c r="J3" s="1" t="str">
         <v/>
       </c>
@@ -559,10 +559,10 @@
         <v/>
       </c>
       <c r="L3" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M3" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -585,43 +585,43 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B4" s="1">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C4" s="1">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="D4" s="1">
+        <v>60</v>
+      </c>
+      <c r="E4" s="1">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1">
         <v>30</v>
-      </c>
-      <c r="E4" s="1">
-        <v>80</v>
-      </c>
-      <c r="F4" s="1">
-        <v>40</v>
       </c>
       <c r="G4" s="1">
         <v>10</v>
       </c>
-      <c r="H4" s="1">
-        <v>60</v>
-      </c>
-      <c r="I4" s="1">
-        <v>20</v>
-      </c>
-      <c r="J4" s="1">
-        <v>20</v>
-      </c>
-      <c r="K4" s="1">
-        <v>10</v>
+      <c r="H4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K4" s="1" t="str">
+        <v/>
       </c>
       <c r="L4" s="1">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M4" s="1">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -630,7 +630,7 @@
         <v>yes</v>
       </c>
       <c r="P4" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="Q4" s="1" t="str">
         <v>no</v>
@@ -639,48 +639,48 @@
         <v/>
       </c>
       <c r="S4" s="1" t="str">
-        <v>Sugar dip snack</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B5" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C5" s="1">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D5" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1">
+        <v>80</v>
+      </c>
+      <c r="F5" s="1">
+        <v>40</v>
+      </c>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>60</v>
+      </c>
+      <c r="I5" s="1">
         <v>20</v>
       </c>
-      <c r="F5" s="1">
-        <v>45</v>
-      </c>
-      <c r="G5" s="1">
-        <v>5</v>
-      </c>
-      <c r="H5" s="1">
-        <v>50</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
+        <v>20</v>
+      </c>
+      <c r="K5" s="1">
         <v>10</v>
       </c>
-      <c r="J5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K5" s="1" t="str">
-        <v/>
-      </c>
       <c r="L5" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M5" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -689,7 +689,7 @@
         <v>yes</v>
       </c>
       <c r="P5" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q5" s="1" t="str">
         <v>no</v>
@@ -698,37 +698,37 @@
         <v/>
       </c>
       <c r="S5" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B6" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C6" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D6" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G6" s="1">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1">
+        <v>50</v>
+      </c>
+      <c r="I6" s="1">
         <v>10</v>
       </c>
-      <c r="H6" s="1">
-        <v>40</v>
-      </c>
-      <c r="I6" s="1">
-        <v>15</v>
-      </c>
       <c r="J6" s="1" t="str">
         <v/>
       </c>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="L6" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M6" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -762,43 +762,43 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B7" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C7" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D7" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1">
         <v>40</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>15</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>80</v>
-      </c>
-      <c r="J7" s="1">
-        <v>30</v>
-      </c>
-      <c r="K7" s="1">
-        <v>5</v>
+      <c r="J7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K7" s="1" t="str">
+        <v/>
       </c>
       <c r="L7" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M7" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -816,18 +816,18 @@
         <v/>
       </c>
       <c r="S7" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B8" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C8" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D8" s="1">
         <v>8</v>
@@ -836,28 +836,28 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1">
         <v>15</v>
       </c>
       <c r="H8" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>15</v>
-      </c>
-      <c r="J8" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K8" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J8" s="1">
+        <v>30</v>
+      </c>
+      <c r="K8" s="1">
+        <v>5</v>
       </c>
       <c r="L8" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M8" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N8" s="1" t="str">
         <v>no</v>
@@ -875,48 +875,48 @@
         <v/>
       </c>
       <c r="S8" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B9" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C9" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D9" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G9" s="1">
         <v>15</v>
       </c>
       <c r="H9" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I9" s="1">
-        <v>20</v>
-      </c>
-      <c r="J9" s="1">
-        <v>20</v>
-      </c>
-      <c r="K9" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K9" s="1" t="str">
+        <v/>
       </c>
       <c r="L9" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M9" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N9" s="1" t="str">
         <v>no</v>
@@ -939,43 +939,43 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B10" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C10" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D10" s="1">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1">
         <v>40</v>
       </c>
-      <c r="E10" s="1">
-        <v>10</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H10" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I10" s="1">
         <v>20</v>
       </c>
-      <c r="J10" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K10" s="1" t="str">
-        <v/>
+      <c r="J10" s="1">
+        <v>20</v>
+      </c>
+      <c r="K10" s="1">
+        <v>2</v>
       </c>
       <c r="L10" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M10" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N10" s="1" t="str">
         <v>no</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B11" s="1">
         <v>287</v>
@@ -1007,22 +1007,22 @@
         <v>198</v>
       </c>
       <c r="D11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11" s="1">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>60</v>
       </c>
-      <c r="E11" s="1">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1">
-        <v>60</v>
-      </c>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
-      <c r="H11" s="1">
-        <v>40</v>
-      </c>
       <c r="I11" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J11" s="1" t="str">
         <v/>
@@ -1031,10 +1031,10 @@
         <v/>
       </c>
       <c r="L11" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M11" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N11" s="1" t="str">
         <v>no</v>
@@ -1052,12 +1052,71 @@
         <v/>
       </c>
       <c r="S11" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B12" s="1">
+        <v>287</v>
+      </c>
+      <c r="C12" s="1">
+        <v>198</v>
+      </c>
+      <c r="D12" s="1">
+        <v>60</v>
+      </c>
+      <c r="E12" s="1">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1">
+        <v>60</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>40</v>
+      </c>
+      <c r="I12" s="1">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K12" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L12" s="1">
+        <v>160</v>
+      </c>
+      <c r="M12" s="1">
+        <v>35</v>
+      </c>
+      <c r="N12" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O12" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P12" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q12" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R12" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S12" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -472,8 +472,8 @@
       <c r="B2" s="1" t="str">
         <v/>
       </c>
-      <c r="C2" s="1" t="str">
-        <v/>
+      <c r="C2" s="1">
+        <v>150</v>
       </c>
       <c r="D2" s="1">
         <v>15</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -487,11 +487,11 @@
       <c r="G2" s="1">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="H2" s="1">
+        <v>60</v>
+      </c>
+      <c r="I2" s="1">
+        <v>15</v>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="M2" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -469,8 +469,8 @@
       <c r="A2" s="1" t="str">
         <v>2026-05-12</v>
       </c>
-      <c r="B2" s="1" t="str">
-        <v/>
+      <c r="B2" s="1">
+        <v>286</v>
       </c>
       <c r="C2" s="1">
         <v>150</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,49 +467,49 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="B2" s="1">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C2" s="1">
-        <v>150</v>
-      </c>
-      <c r="D2" s="1">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1">
+        <v>144</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" s="1">
-        <v>60</v>
-      </c>
-      <c r="G2" s="1">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1">
-        <v>60</v>
-      </c>
-      <c r="I2" s="1">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L2" s="1">
-        <v>135</v>
-      </c>
       <c r="M2" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>
@@ -526,13 +526,13 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="B3" s="1" t="str">
-        <v/>
+        <v>2026-05-12</v>
+      </c>
+      <c r="B3" s="1">
+        <v>286</v>
       </c>
       <c r="C3" s="1">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="D3" s="1">
         <v>15</v>
@@ -541,16 +541,16 @@
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G3" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H3" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I3" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J3" s="1" t="str">
         <v/>
@@ -559,10 +559,10 @@
         <v/>
       </c>
       <c r="L3" s="1">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="M3" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -585,32 +585,32 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="B4" s="1">
-        <v>282</v>
+        <v>2026-05-11</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <v/>
       </c>
       <c r="C4" s="1">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="D4" s="1">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
+        <v>50</v>
+      </c>
+      <c r="G4" s="1">
+        <v>40</v>
+      </c>
+      <c r="H4" s="1">
         <v>30</v>
       </c>
-      <c r="G4" s="1">
+      <c r="I4" s="1">
         <v>10</v>
       </c>
-      <c r="H4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I4" s="1" t="str">
-        <v/>
-      </c>
       <c r="J4" s="1" t="str">
         <v/>
       </c>
@@ -618,10 +618,10 @@
         <v/>
       </c>
       <c r="L4" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M4" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -644,43 +644,43 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B5" s="1">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C5" s="1">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="D5" s="1">
+        <v>60</v>
+      </c>
+      <c r="E5" s="1">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1">
         <v>30</v>
-      </c>
-      <c r="E5" s="1">
-        <v>80</v>
-      </c>
-      <c r="F5" s="1">
-        <v>40</v>
       </c>
       <c r="G5" s="1">
         <v>10</v>
       </c>
-      <c r="H5" s="1">
-        <v>60</v>
-      </c>
-      <c r="I5" s="1">
-        <v>20</v>
-      </c>
-      <c r="J5" s="1">
-        <v>20</v>
-      </c>
-      <c r="K5" s="1">
-        <v>10</v>
+      <c r="H5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K5" s="1" t="str">
+        <v/>
       </c>
       <c r="L5" s="1">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M5" s="1">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -689,7 +689,7 @@
         <v>yes</v>
       </c>
       <c r="P5" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="Q5" s="1" t="str">
         <v>no</v>
@@ -698,48 +698,48 @@
         <v/>
       </c>
       <c r="S5" s="1" t="str">
-        <v>Sugar dip snack</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B6" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C6" s="1">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D6" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E6" s="1">
+        <v>80</v>
+      </c>
+      <c r="F6" s="1">
+        <v>40</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>60</v>
+      </c>
+      <c r="I6" s="1">
         <v>20</v>
       </c>
-      <c r="F6" s="1">
-        <v>45</v>
-      </c>
-      <c r="G6" s="1">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1">
-        <v>50</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
+        <v>20</v>
+      </c>
+      <c r="K6" s="1">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K6" s="1" t="str">
-        <v/>
-      </c>
       <c r="L6" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M6" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -748,7 +748,7 @@
         <v>yes</v>
       </c>
       <c r="P6" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q6" s="1" t="str">
         <v>no</v>
@@ -757,37 +757,37 @@
         <v/>
       </c>
       <c r="S6" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B7" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C7" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D7" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G7" s="1">
+        <v>5</v>
+      </c>
+      <c r="H7" s="1">
+        <v>50</v>
+      </c>
+      <c r="I7" s="1">
         <v>10</v>
       </c>
-      <c r="H7" s="1">
-        <v>40</v>
-      </c>
-      <c r="I7" s="1">
-        <v>15</v>
-      </c>
       <c r="J7" s="1" t="str">
         <v/>
       </c>
@@ -795,10 +795,10 @@
         <v/>
       </c>
       <c r="L7" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M7" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -821,43 +821,43 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B8" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C8" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D8" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
         <v>40</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>15</v>
       </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>80</v>
-      </c>
-      <c r="J8" s="1">
-        <v>30</v>
-      </c>
-      <c r="K8" s="1">
-        <v>5</v>
+      <c r="J8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K8" s="1" t="str">
+        <v/>
       </c>
       <c r="L8" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M8" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N8" s="1" t="str">
         <v>no</v>
@@ -875,18 +875,18 @@
         <v/>
       </c>
       <c r="S8" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B9" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C9" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
@@ -895,28 +895,28 @@
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G9" s="1">
         <v>15</v>
       </c>
       <c r="H9" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>15</v>
-      </c>
-      <c r="J9" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K9" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J9" s="1">
+        <v>30</v>
+      </c>
+      <c r="K9" s="1">
+        <v>5</v>
       </c>
       <c r="L9" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M9" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N9" s="1" t="str">
         <v>no</v>
@@ -934,48 +934,48 @@
         <v/>
       </c>
       <c r="S9" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B10" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C10" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D10" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G10" s="1">
         <v>15</v>
       </c>
       <c r="H10" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I10" s="1">
-        <v>20</v>
-      </c>
-      <c r="J10" s="1">
-        <v>20</v>
-      </c>
-      <c r="K10" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K10" s="1" t="str">
+        <v/>
       </c>
       <c r="L10" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M10" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N10" s="1" t="str">
         <v>no</v>
@@ -998,43 +998,43 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B11" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C11" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D11" s="1">
+        <v>30</v>
+      </c>
+      <c r="E11" s="1">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1">
         <v>40</v>
       </c>
-      <c r="E11" s="1">
-        <v>10</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H11" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I11" s="1">
         <v>20</v>
       </c>
-      <c r="J11" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K11" s="1" t="str">
-        <v/>
+      <c r="J11" s="1">
+        <v>20</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2</v>
       </c>
       <c r="L11" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M11" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N11" s="1" t="str">
         <v>no</v>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B12" s="1">
         <v>287</v>
@@ -1066,22 +1066,22 @@
         <v>198</v>
       </c>
       <c r="D12" s="1">
+        <v>40</v>
+      </c>
+      <c r="E12" s="1">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>60</v>
       </c>
-      <c r="E12" s="1">
-        <v>15</v>
-      </c>
-      <c r="F12" s="1">
-        <v>60</v>
-      </c>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>40</v>
-      </c>
       <c r="I12" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J12" s="1" t="str">
         <v/>
@@ -1090,10 +1090,10 @@
         <v/>
       </c>
       <c r="L12" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M12" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N12" s="1" t="str">
         <v>no</v>
@@ -1114,9 +1114,68 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B13" s="1">
+        <v>287</v>
+      </c>
+      <c r="C13" s="1">
+        <v>198</v>
+      </c>
+      <c r="D13" s="1">
+        <v>60</v>
+      </c>
+      <c r="E13" s="1">
+        <v>15</v>
+      </c>
+      <c r="F13" s="1">
+        <v>60</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1">
+        <v>40</v>
+      </c>
+      <c r="I13" s="1">
+        <v>10</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L13" s="1">
+        <v>160</v>
+      </c>
+      <c r="M13" s="1">
+        <v>35</v>
+      </c>
+      <c r="N13" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O13" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P13" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q13" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S13" s="1" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -475,23 +475,23 @@
       <c r="C2" s="1">
         <v>144</v>
       </c>
-      <c r="D2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="D2" s="1">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1">
+        <v>60</v>
+      </c>
+      <c r="I2" s="1">
+        <v>10</v>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -493,17 +493,17 @@
       <c r="I2" s="1">
         <v>10</v>
       </c>
-      <c r="J2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K2" s="1" t="str">
-        <v/>
+      <c r="J2" s="1">
+        <v>60</v>
+      </c>
+      <c r="K2" s="1">
+        <v>10</v>
       </c>
       <c r="L2" s="1">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="M2" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S14"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,43 +467,43 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B2" s="1">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C2" s="1">
-        <v>144</v>
-      </c>
-      <c r="D2" s="1">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1">
+        <v>242</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" s="1">
-        <v>30</v>
-      </c>
-      <c r="G2" s="1">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1">
-        <v>60</v>
-      </c>
-      <c r="I2" s="1">
-        <v>10</v>
-      </c>
-      <c r="J2" s="1">
-        <v>60</v>
-      </c>
-      <c r="K2" s="1">
-        <v>10</v>
-      </c>
-      <c r="L2" s="1">
-        <v>165</v>
-      </c>
       <c r="M2" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
@@ -526,13 +526,13 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="B3" s="1">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C3" s="1">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D3" s="1">
         <v>15</v>
@@ -541,25 +541,25 @@
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H3" s="1">
         <v>60</v>
       </c>
       <c r="I3" s="1">
-        <v>15</v>
-      </c>
-      <c r="J3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K3" s="1" t="str">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="J3" s="1">
+        <v>60</v>
+      </c>
+      <c r="K3" s="1">
+        <v>10</v>
       </c>
       <c r="L3" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="M3" s="1">
         <v>25</v>
@@ -585,13 +585,13 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="B4" s="1" t="str">
-        <v/>
+        <v>2026-05-12</v>
+      </c>
+      <c r="B4" s="1">
+        <v>286</v>
       </c>
       <c r="C4" s="1">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="D4" s="1">
         <v>15</v>
@@ -600,16 +600,16 @@
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G4" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H4" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I4" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J4" s="1" t="str">
         <v/>
@@ -618,10 +618,10 @@
         <v/>
       </c>
       <c r="L4" s="1">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="M4" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -644,32 +644,32 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="B5" s="1">
-        <v>282</v>
+        <v>2026-05-11</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <v/>
       </c>
       <c r="C5" s="1">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="D5" s="1">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
+        <v>50</v>
+      </c>
+      <c r="G5" s="1">
+        <v>40</v>
+      </c>
+      <c r="H5" s="1">
         <v>30</v>
       </c>
-      <c r="G5" s="1">
+      <c r="I5" s="1">
         <v>10</v>
       </c>
-      <c r="H5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="1" t="str">
-        <v/>
-      </c>
       <c r="J5" s="1" t="str">
         <v/>
       </c>
@@ -677,10 +677,10 @@
         <v/>
       </c>
       <c r="L5" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M5" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -703,43 +703,43 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B6" s="1">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C6" s="1">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="D6" s="1">
+        <v>60</v>
+      </c>
+      <c r="E6" s="1">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1">
         <v>30</v>
-      </c>
-      <c r="E6" s="1">
-        <v>80</v>
-      </c>
-      <c r="F6" s="1">
-        <v>40</v>
       </c>
       <c r="G6" s="1">
         <v>10</v>
       </c>
-      <c r="H6" s="1">
-        <v>60</v>
-      </c>
-      <c r="I6" s="1">
-        <v>20</v>
-      </c>
-      <c r="J6" s="1">
-        <v>20</v>
-      </c>
-      <c r="K6" s="1">
-        <v>10</v>
+      <c r="H6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K6" s="1" t="str">
+        <v/>
       </c>
       <c r="L6" s="1">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M6" s="1">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -748,7 +748,7 @@
         <v>yes</v>
       </c>
       <c r="P6" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="Q6" s="1" t="str">
         <v>no</v>
@@ -757,48 +757,48 @@
         <v/>
       </c>
       <c r="S6" s="1" t="str">
-        <v>Sugar dip snack</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B7" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C7" s="1">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D7" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1">
+        <v>80</v>
+      </c>
+      <c r="F7" s="1">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1">
+        <v>60</v>
+      </c>
+      <c r="I7" s="1">
         <v>20</v>
       </c>
-      <c r="F7" s="1">
-        <v>45</v>
-      </c>
-      <c r="G7" s="1">
-        <v>5</v>
-      </c>
-      <c r="H7" s="1">
-        <v>50</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
+        <v>20</v>
+      </c>
+      <c r="K7" s="1">
         <v>10</v>
       </c>
-      <c r="J7" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K7" s="1" t="str">
-        <v/>
-      </c>
       <c r="L7" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M7" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -807,7 +807,7 @@
         <v>yes</v>
       </c>
       <c r="P7" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q7" s="1" t="str">
         <v>no</v>
@@ -816,37 +816,37 @@
         <v/>
       </c>
       <c r="S7" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B8" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C8" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D8" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G8" s="1">
+        <v>5</v>
+      </c>
+      <c r="H8" s="1">
+        <v>50</v>
+      </c>
+      <c r="I8" s="1">
         <v>10</v>
       </c>
-      <c r="H8" s="1">
-        <v>40</v>
-      </c>
-      <c r="I8" s="1">
-        <v>15</v>
-      </c>
       <c r="J8" s="1" t="str">
         <v/>
       </c>
@@ -854,10 +854,10 @@
         <v/>
       </c>
       <c r="L8" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M8" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N8" s="1" t="str">
         <v>no</v>
@@ -880,43 +880,43 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B9" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C9" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D9" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1">
+        <v>11</v>
+      </c>
+      <c r="F9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
         <v>40</v>
       </c>
-      <c r="G9" s="1">
+      <c r="I9" s="1">
         <v>15</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>80</v>
-      </c>
-      <c r="J9" s="1">
-        <v>30</v>
-      </c>
-      <c r="K9" s="1">
-        <v>5</v>
+      <c r="J9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K9" s="1" t="str">
+        <v/>
       </c>
       <c r="L9" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M9" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N9" s="1" t="str">
         <v>no</v>
@@ -934,18 +934,18 @@
         <v/>
       </c>
       <c r="S9" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B10" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C10" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
@@ -954,28 +954,28 @@
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G10" s="1">
         <v>15</v>
       </c>
       <c r="H10" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>15</v>
-      </c>
-      <c r="J10" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K10" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J10" s="1">
+        <v>30</v>
+      </c>
+      <c r="K10" s="1">
+        <v>5</v>
       </c>
       <c r="L10" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M10" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N10" s="1" t="str">
         <v>no</v>
@@ -993,48 +993,48 @@
         <v/>
       </c>
       <c r="S10" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B11" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C11" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D11" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G11" s="1">
         <v>15</v>
       </c>
       <c r="H11" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I11" s="1">
-        <v>20</v>
-      </c>
-      <c r="J11" s="1">
-        <v>20</v>
-      </c>
-      <c r="K11" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J11" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K11" s="1" t="str">
+        <v/>
       </c>
       <c r="L11" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M11" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N11" s="1" t="str">
         <v>no</v>
@@ -1057,43 +1057,43 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B12" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C12" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D12" s="1">
+        <v>30</v>
+      </c>
+      <c r="E12" s="1">
+        <v>5</v>
+      </c>
+      <c r="F12" s="1">
         <v>40</v>
       </c>
-      <c r="E12" s="1">
-        <v>10</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H12" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I12" s="1">
         <v>20</v>
       </c>
-      <c r="J12" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K12" s="1" t="str">
-        <v/>
+      <c r="J12" s="1">
+        <v>20</v>
+      </c>
+      <c r="K12" s="1">
+        <v>2</v>
       </c>
       <c r="L12" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M12" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N12" s="1" t="str">
         <v>no</v>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B13" s="1">
         <v>287</v>
@@ -1125,57 +1125,116 @@
         <v>198</v>
       </c>
       <c r="D13" s="1">
+        <v>40</v>
+      </c>
+      <c r="E13" s="1">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <v>60</v>
       </c>
-      <c r="E13" s="1">
+      <c r="I13" s="1">
+        <v>20</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L13" s="1">
+        <v>100</v>
+      </c>
+      <c r="M13" s="1">
+        <v>30</v>
+      </c>
+      <c r="N13" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O13" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P13" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q13" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S13" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B14" s="1">
+        <v>287</v>
+      </c>
+      <c r="C14" s="1">
+        <v>198</v>
+      </c>
+      <c r="D14" s="1">
+        <v>60</v>
+      </c>
+      <c r="E14" s="1">
         <v>15</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F14" s="1">
         <v>60</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G14" s="1">
         <v>10</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H14" s="1">
         <v>40</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I14" s="1">
         <v>10</v>
       </c>
-      <c r="J13" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K13" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L13" s="1">
+      <c r="J14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L14" s="1">
         <v>160</v>
       </c>
-      <c r="M13" s="1">
+      <c r="M14" s="1">
         <v>35</v>
       </c>
-      <c r="N13" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="O13" s="1" t="str">
-        <v>yes</v>
-      </c>
-      <c r="P13" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="Q13" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="R13" s="1" t="str">
-        <v/>
-      </c>
-      <c r="S13" s="1" t="str">
+      <c r="N14" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O14" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P14" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q14" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S14" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -475,17 +475,17 @@
       <c r="C2" s="1">
         <v>242</v>
       </c>
-      <c r="D2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
+      <c r="D2" s="1">
+        <v>40</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1">
+        <v>60</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5</v>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,25 +467,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-15</v>
       </c>
       <c r="B2" s="1">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C2" s="1">
-        <v>242</v>
-      </c>
-      <c r="D2" s="1">
-        <v>40</v>
-      </c>
-      <c r="E2" s="1">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1">
-        <v>60</v>
-      </c>
-      <c r="G2" s="1">
-        <v>5</v>
+        <v>213</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v/>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>
@@ -526,43 +526,43 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B3" s="1">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C3" s="1">
-        <v>144</v>
+        <v>242</v>
       </c>
       <c r="D3" s="1">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E3" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G3" s="1">
         <v>5</v>
       </c>
-      <c r="H3" s="1">
-        <v>60</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="H3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L3" s="1">
+        <v>100</v>
+      </c>
+      <c r="M3" s="1">
         <v>10</v>
-      </c>
-      <c r="J3" s="1">
-        <v>60</v>
-      </c>
-      <c r="K3" s="1">
-        <v>10</v>
-      </c>
-      <c r="L3" s="1">
-        <v>165</v>
-      </c>
-      <c r="M3" s="1">
-        <v>25</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -585,13 +585,13 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="B4" s="1">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C4" s="1">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D4" s="1">
         <v>15</v>
@@ -600,25 +600,25 @@
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H4" s="1">
         <v>60</v>
       </c>
       <c r="I4" s="1">
-        <v>15</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K4" s="1" t="str">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="J4" s="1">
+        <v>60</v>
+      </c>
+      <c r="K4" s="1">
+        <v>10</v>
       </c>
       <c r="L4" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="M4" s="1">
         <v>25</v>
@@ -644,13 +644,13 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="B5" s="1" t="str">
-        <v/>
+        <v>2026-05-12</v>
+      </c>
+      <c r="B5" s="1">
+        <v>286</v>
       </c>
       <c r="C5" s="1">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="D5" s="1">
         <v>15</v>
@@ -659,16 +659,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G5" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H5" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I5" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J5" s="1" t="str">
         <v/>
@@ -677,10 +677,10 @@
         <v/>
       </c>
       <c r="L5" s="1">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="M5" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -703,32 +703,32 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="B6" s="1">
-        <v>282</v>
+        <v>2026-05-11</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <v/>
       </c>
       <c r="C6" s="1">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="D6" s="1">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1">
+        <v>40</v>
+      </c>
+      <c r="H6" s="1">
         <v>30</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>10</v>
       </c>
-      <c r="H6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I6" s="1" t="str">
-        <v/>
-      </c>
       <c r="J6" s="1" t="str">
         <v/>
       </c>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="L6" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M6" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -762,43 +762,43 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B7" s="1">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C7" s="1">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="D7" s="1">
+        <v>60</v>
+      </c>
+      <c r="E7" s="1">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1">
         <v>30</v>
-      </c>
-      <c r="E7" s="1">
-        <v>80</v>
-      </c>
-      <c r="F7" s="1">
-        <v>40</v>
       </c>
       <c r="G7" s="1">
         <v>10</v>
       </c>
-      <c r="H7" s="1">
-        <v>60</v>
-      </c>
-      <c r="I7" s="1">
-        <v>20</v>
-      </c>
-      <c r="J7" s="1">
-        <v>20</v>
-      </c>
-      <c r="K7" s="1">
-        <v>10</v>
+      <c r="H7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K7" s="1" t="str">
+        <v/>
       </c>
       <c r="L7" s="1">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M7" s="1">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -807,7 +807,7 @@
         <v>yes</v>
       </c>
       <c r="P7" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="Q7" s="1" t="str">
         <v>no</v>
@@ -816,48 +816,48 @@
         <v/>
       </c>
       <c r="S7" s="1" t="str">
-        <v>Sugar dip snack</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B8" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C8" s="1">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D8" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E8" s="1">
+        <v>80</v>
+      </c>
+      <c r="F8" s="1">
+        <v>40</v>
+      </c>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1">
+        <v>60</v>
+      </c>
+      <c r="I8" s="1">
         <v>20</v>
       </c>
-      <c r="F8" s="1">
-        <v>45</v>
-      </c>
-      <c r="G8" s="1">
-        <v>5</v>
-      </c>
-      <c r="H8" s="1">
-        <v>50</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
+        <v>20</v>
+      </c>
+      <c r="K8" s="1">
         <v>10</v>
       </c>
-      <c r="J8" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K8" s="1" t="str">
-        <v/>
-      </c>
       <c r="L8" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M8" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="N8" s="1" t="str">
         <v>no</v>
@@ -866,7 +866,7 @@
         <v>yes</v>
       </c>
       <c r="P8" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q8" s="1" t="str">
         <v>no</v>
@@ -875,37 +875,37 @@
         <v/>
       </c>
       <c r="S8" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B9" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C9" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D9" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G9" s="1">
+        <v>5</v>
+      </c>
+      <c r="H9" s="1">
+        <v>50</v>
+      </c>
+      <c r="I9" s="1">
         <v>10</v>
       </c>
-      <c r="H9" s="1">
-        <v>40</v>
-      </c>
-      <c r="I9" s="1">
-        <v>15</v>
-      </c>
       <c r="J9" s="1" t="str">
         <v/>
       </c>
@@ -913,10 +913,10 @@
         <v/>
       </c>
       <c r="L9" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M9" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N9" s="1" t="str">
         <v>no</v>
@@ -939,43 +939,43 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B10" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C10" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D10" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1">
+        <v>11</v>
+      </c>
+      <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
         <v>40</v>
       </c>
-      <c r="G10" s="1">
+      <c r="I10" s="1">
         <v>15</v>
       </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>80</v>
-      </c>
-      <c r="J10" s="1">
-        <v>30</v>
-      </c>
-      <c r="K10" s="1">
-        <v>5</v>
+      <c r="J10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K10" s="1" t="str">
+        <v/>
       </c>
       <c r="L10" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M10" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N10" s="1" t="str">
         <v>no</v>
@@ -993,18 +993,18 @@
         <v/>
       </c>
       <c r="S10" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B11" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C11" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D11" s="1">
         <v>8</v>
@@ -1013,28 +1013,28 @@
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1">
         <v>15</v>
       </c>
       <c r="H11" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>15</v>
-      </c>
-      <c r="J11" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K11" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J11" s="1">
+        <v>30</v>
+      </c>
+      <c r="K11" s="1">
+        <v>5</v>
       </c>
       <c r="L11" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M11" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N11" s="1" t="str">
         <v>no</v>
@@ -1052,48 +1052,48 @@
         <v/>
       </c>
       <c r="S11" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B12" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C12" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D12" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G12" s="1">
         <v>15</v>
       </c>
       <c r="H12" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I12" s="1">
-        <v>20</v>
-      </c>
-      <c r="J12" s="1">
-        <v>20</v>
-      </c>
-      <c r="K12" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J12" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K12" s="1" t="str">
+        <v/>
       </c>
       <c r="L12" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M12" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N12" s="1" t="str">
         <v>no</v>
@@ -1116,43 +1116,43 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B13" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C13" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D13" s="1">
+        <v>30</v>
+      </c>
+      <c r="E13" s="1">
+        <v>5</v>
+      </c>
+      <c r="F13" s="1">
         <v>40</v>
       </c>
-      <c r="E13" s="1">
-        <v>10</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H13" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I13" s="1">
         <v>20</v>
       </c>
-      <c r="J13" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K13" s="1" t="str">
-        <v/>
+      <c r="J13" s="1">
+        <v>20</v>
+      </c>
+      <c r="K13" s="1">
+        <v>2</v>
       </c>
       <c r="L13" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M13" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N13" s="1" t="str">
         <v>no</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B14" s="1">
         <v>287</v>
@@ -1184,57 +1184,116 @@
         <v>198</v>
       </c>
       <c r="D14" s="1">
+        <v>40</v>
+      </c>
+      <c r="E14" s="1">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>60</v>
       </c>
-      <c r="E14" s="1">
+      <c r="I14" s="1">
+        <v>20</v>
+      </c>
+      <c r="J14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L14" s="1">
+        <v>100</v>
+      </c>
+      <c r="M14" s="1">
+        <v>30</v>
+      </c>
+      <c r="N14" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O14" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P14" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q14" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S14" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B15" s="1">
+        <v>287</v>
+      </c>
+      <c r="C15" s="1">
+        <v>198</v>
+      </c>
+      <c r="D15" s="1">
+        <v>60</v>
+      </c>
+      <c r="E15" s="1">
         <v>15</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F15" s="1">
         <v>60</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G15" s="1">
         <v>10</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H15" s="1">
         <v>40</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I15" s="1">
         <v>10</v>
       </c>
-      <c r="J14" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K14" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L14" s="1">
+      <c r="J15" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K15" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L15" s="1">
         <v>160</v>
       </c>
-      <c r="M14" s="1">
+      <c r="M15" s="1">
         <v>35</v>
       </c>
-      <c r="N14" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="O14" s="1" t="str">
-        <v>yes</v>
-      </c>
-      <c r="P14" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="Q14" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="R14" s="1" t="str">
-        <v/>
-      </c>
-      <c r="S14" s="1" t="str">
+      <c r="N15" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O15" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P15" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q15" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R15" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S15" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S16"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,13 +467,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="B2" s="1">
-        <v>281</v>
+        <v>2026-05-16</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v/>
       </c>
       <c r="C2" s="1">
-        <v>213</v>
+        <v>277</v>
       </c>
       <c r="D2" s="1" t="str">
         <v/>
@@ -526,25 +526,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-15</v>
       </c>
       <c r="B3" s="1">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C3" s="1">
-        <v>242</v>
-      </c>
-      <c r="D3" s="1">
-        <v>40</v>
-      </c>
-      <c r="E3" s="1">
-        <v>5</v>
-      </c>
-      <c r="F3" s="1">
-        <v>60</v>
-      </c>
-      <c r="G3" s="1">
-        <v>5</v>
+        <v>213</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G3" s="1" t="str">
+        <v/>
       </c>
       <c r="H3" s="1" t="str">
         <v/>
@@ -559,16 +559,16 @@
         <v/>
       </c>
       <c r="L3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O3" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P3" s="1" t="str">
         <v>no</v>
@@ -585,43 +585,43 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B4" s="1">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C4" s="1">
-        <v>144</v>
+        <v>242</v>
       </c>
       <c r="D4" s="1">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G4" s="1">
         <v>5</v>
       </c>
-      <c r="H4" s="1">
-        <v>60</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="H4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L4" s="1">
+        <v>100</v>
+      </c>
+      <c r="M4" s="1">
         <v>10</v>
-      </c>
-      <c r="J4" s="1">
-        <v>60</v>
-      </c>
-      <c r="K4" s="1">
-        <v>10</v>
-      </c>
-      <c r="L4" s="1">
-        <v>165</v>
-      </c>
-      <c r="M4" s="1">
-        <v>25</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
@@ -644,13 +644,13 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="B5" s="1">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C5" s="1">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D5" s="1">
         <v>15</v>
@@ -659,25 +659,25 @@
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H5" s="1">
         <v>60</v>
       </c>
       <c r="I5" s="1">
-        <v>15</v>
-      </c>
-      <c r="J5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K5" s="1" t="str">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="J5" s="1">
+        <v>60</v>
+      </c>
+      <c r="K5" s="1">
+        <v>10</v>
       </c>
       <c r="L5" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="M5" s="1">
         <v>25</v>
@@ -703,13 +703,13 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="B6" s="1" t="str">
-        <v/>
+        <v>2026-05-12</v>
+      </c>
+      <c r="B6" s="1">
+        <v>286</v>
       </c>
       <c r="C6" s="1">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="D6" s="1">
         <v>15</v>
@@ -718,16 +718,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G6" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I6" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J6" s="1" t="str">
         <v/>
@@ -736,10 +736,10 @@
         <v/>
       </c>
       <c r="L6" s="1">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="M6" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -762,32 +762,32 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="B7" s="1">
-        <v>282</v>
+        <v>2026-05-11</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <v/>
       </c>
       <c r="C7" s="1">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="D7" s="1">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
+        <v>50</v>
+      </c>
+      <c r="G7" s="1">
+        <v>40</v>
+      </c>
+      <c r="H7" s="1">
         <v>30</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>10</v>
       </c>
-      <c r="H7" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I7" s="1" t="str">
-        <v/>
-      </c>
       <c r="J7" s="1" t="str">
         <v/>
       </c>
@@ -795,10 +795,10 @@
         <v/>
       </c>
       <c r="L7" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M7" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -821,43 +821,43 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B8" s="1">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C8" s="1">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="D8" s="1">
+        <v>60</v>
+      </c>
+      <c r="E8" s="1">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1">
         <v>30</v>
-      </c>
-      <c r="E8" s="1">
-        <v>80</v>
-      </c>
-      <c r="F8" s="1">
-        <v>40</v>
       </c>
       <c r="G8" s="1">
         <v>10</v>
       </c>
-      <c r="H8" s="1">
-        <v>60</v>
-      </c>
-      <c r="I8" s="1">
-        <v>20</v>
-      </c>
-      <c r="J8" s="1">
-        <v>20</v>
-      </c>
-      <c r="K8" s="1">
-        <v>10</v>
+      <c r="H8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K8" s="1" t="str">
+        <v/>
       </c>
       <c r="L8" s="1">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M8" s="1">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="N8" s="1" t="str">
         <v>no</v>
@@ -866,7 +866,7 @@
         <v>yes</v>
       </c>
       <c r="P8" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="Q8" s="1" t="str">
         <v>no</v>
@@ -875,48 +875,48 @@
         <v/>
       </c>
       <c r="S8" s="1" t="str">
-        <v>Sugar dip snack</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B9" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C9" s="1">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D9" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1">
+        <v>80</v>
+      </c>
+      <c r="F9" s="1">
+        <v>40</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>60</v>
+      </c>
+      <c r="I9" s="1">
         <v>20</v>
       </c>
-      <c r="F9" s="1">
-        <v>45</v>
-      </c>
-      <c r="G9" s="1">
-        <v>5</v>
-      </c>
-      <c r="H9" s="1">
-        <v>50</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
+        <v>20</v>
+      </c>
+      <c r="K9" s="1">
         <v>10</v>
       </c>
-      <c r="J9" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K9" s="1" t="str">
-        <v/>
-      </c>
       <c r="L9" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M9" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="N9" s="1" t="str">
         <v>no</v>
@@ -925,7 +925,7 @@
         <v>yes</v>
       </c>
       <c r="P9" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q9" s="1" t="str">
         <v>no</v>
@@ -934,37 +934,37 @@
         <v/>
       </c>
       <c r="S9" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B10" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C10" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D10" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1">
+        <v>50</v>
+      </c>
+      <c r="I10" s="1">
         <v>10</v>
       </c>
-      <c r="H10" s="1">
-        <v>40</v>
-      </c>
-      <c r="I10" s="1">
-        <v>15</v>
-      </c>
       <c r="J10" s="1" t="str">
         <v/>
       </c>
@@ -972,10 +972,10 @@
         <v/>
       </c>
       <c r="L10" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M10" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N10" s="1" t="str">
         <v>no</v>
@@ -998,43 +998,43 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B11" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C11" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D11" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E11" s="1">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
         <v>40</v>
       </c>
-      <c r="G11" s="1">
+      <c r="I11" s="1">
         <v>15</v>
       </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>80</v>
-      </c>
-      <c r="J11" s="1">
-        <v>30</v>
-      </c>
-      <c r="K11" s="1">
-        <v>5</v>
+      <c r="J11" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K11" s="1" t="str">
+        <v/>
       </c>
       <c r="L11" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M11" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N11" s="1" t="str">
         <v>no</v>
@@ -1052,18 +1052,18 @@
         <v/>
       </c>
       <c r="S11" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B12" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C12" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D12" s="1">
         <v>8</v>
@@ -1072,28 +1072,28 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G12" s="1">
         <v>15</v>
       </c>
       <c r="H12" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>15</v>
-      </c>
-      <c r="J12" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K12" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J12" s="1">
+        <v>30</v>
+      </c>
+      <c r="K12" s="1">
+        <v>5</v>
       </c>
       <c r="L12" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M12" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N12" s="1" t="str">
         <v>no</v>
@@ -1111,48 +1111,48 @@
         <v/>
       </c>
       <c r="S12" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B13" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C13" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D13" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G13" s="1">
         <v>15</v>
       </c>
       <c r="H13" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I13" s="1">
-        <v>20</v>
-      </c>
-      <c r="J13" s="1">
-        <v>20</v>
-      </c>
-      <c r="K13" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K13" s="1" t="str">
+        <v/>
       </c>
       <c r="L13" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M13" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N13" s="1" t="str">
         <v>no</v>
@@ -1175,43 +1175,43 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B14" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C14" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D14" s="1">
+        <v>30</v>
+      </c>
+      <c r="E14" s="1">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1">
         <v>40</v>
       </c>
-      <c r="E14" s="1">
-        <v>10</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H14" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I14" s="1">
         <v>20</v>
       </c>
-      <c r="J14" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K14" s="1" t="str">
-        <v/>
+      <c r="J14" s="1">
+        <v>20</v>
+      </c>
+      <c r="K14" s="1">
+        <v>2</v>
       </c>
       <c r="L14" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M14" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N14" s="1" t="str">
         <v>no</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B15" s="1">
         <v>287</v>
@@ -1243,22 +1243,22 @@
         <v>198</v>
       </c>
       <c r="D15" s="1">
+        <v>40</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
         <v>60</v>
       </c>
-      <c r="E15" s="1">
-        <v>15</v>
-      </c>
-      <c r="F15" s="1">
-        <v>60</v>
-      </c>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>40</v>
-      </c>
       <c r="I15" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J15" s="1" t="str">
         <v/>
@@ -1267,10 +1267,10 @@
         <v/>
       </c>
       <c r="L15" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="M15" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N15" s="1" t="str">
         <v>no</v>
@@ -1291,9 +1291,68 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B16" s="1">
+        <v>287</v>
+      </c>
+      <c r="C16" s="1">
+        <v>198</v>
+      </c>
+      <c r="D16" s="1">
+        <v>60</v>
+      </c>
+      <c r="E16" s="1">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1">
+        <v>60</v>
+      </c>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>40</v>
+      </c>
+      <c r="I16" s="1">
+        <v>10</v>
+      </c>
+      <c r="J16" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K16" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L16" s="1">
+        <v>160</v>
+      </c>
+      <c r="M16" s="1">
+        <v>35</v>
+      </c>
+      <c r="N16" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O16" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P16" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q16" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R16" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S16" s="1" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -565,10 +565,10 @@
         <v>0</v>
       </c>
       <c r="N3" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="O3" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P3" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -469,29 +469,29 @@
       <c r="A2" s="1" t="str">
         <v>2026-05-16</v>
       </c>
-      <c r="B2" s="1" t="str">
-        <v/>
+      <c r="B2" s="1">
+        <v>284</v>
       </c>
       <c r="C2" s="1">
         <v>277</v>
       </c>
-      <c r="D2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="D2" s="1">
+        <v>60</v>
+      </c>
+      <c r="E2" s="1">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>80</v>
+      </c>
+      <c r="I2" s="1">
+        <v>5</v>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S17"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,31 +467,31 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="B2" s="1">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C2" s="1">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="D2" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E2" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1">
-        <v>80</v>
-      </c>
-      <c r="I2" s="1">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v/>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="M2" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>
@@ -526,31 +526,31 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="B3" s="1">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C3" s="1">
-        <v>213</v>
-      </c>
-      <c r="D3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="H3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I3" s="1" t="str">
-        <v/>
+        <v>277</v>
+      </c>
+      <c r="D3" s="1">
+        <v>60</v>
+      </c>
+      <c r="E3" s="1">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>80</v>
+      </c>
+      <c r="I3" s="1">
+        <v>5</v>
       </c>
       <c r="J3" s="1" t="str">
         <v/>
@@ -559,10 +559,10 @@
         <v/>
       </c>
       <c r="L3" s="1">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M3" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>yes</v>
@@ -585,25 +585,25 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-15</v>
       </c>
       <c r="B4" s="1">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C4" s="1">
-        <v>242</v>
-      </c>
-      <c r="D4" s="1">
-        <v>40</v>
-      </c>
-      <c r="E4" s="1">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1">
-        <v>60</v>
-      </c>
-      <c r="G4" s="1">
-        <v>5</v>
+        <v>213</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="1" t="str">
+        <v/>
       </c>
       <c r="H4" s="1" t="str">
         <v/>
@@ -618,13 +618,13 @@
         <v/>
       </c>
       <c r="L4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N4" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="O4" s="1" t="str">
         <v>yes</v>
@@ -644,43 +644,43 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B5" s="1">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C5" s="1">
-        <v>144</v>
+        <v>242</v>
       </c>
       <c r="D5" s="1">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G5" s="1">
         <v>5</v>
       </c>
-      <c r="H5" s="1">
-        <v>60</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="H5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L5" s="1">
+        <v>100</v>
+      </c>
+      <c r="M5" s="1">
         <v>10</v>
-      </c>
-      <c r="J5" s="1">
-        <v>60</v>
-      </c>
-      <c r="K5" s="1">
-        <v>10</v>
-      </c>
-      <c r="L5" s="1">
-        <v>165</v>
-      </c>
-      <c r="M5" s="1">
-        <v>25</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>no</v>
@@ -703,13 +703,13 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="B6" s="1">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C6" s="1">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D6" s="1">
         <v>15</v>
@@ -718,25 +718,25 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G6" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H6" s="1">
         <v>60</v>
       </c>
       <c r="I6" s="1">
-        <v>15</v>
-      </c>
-      <c r="J6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K6" s="1" t="str">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="J6" s="1">
+        <v>60</v>
+      </c>
+      <c r="K6" s="1">
+        <v>10</v>
       </c>
       <c r="L6" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="M6" s="1">
         <v>25</v>
@@ -762,13 +762,13 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="B7" s="1" t="str">
-        <v/>
+        <v>2026-05-12</v>
+      </c>
+      <c r="B7" s="1">
+        <v>286</v>
       </c>
       <c r="C7" s="1">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="D7" s="1">
         <v>15</v>
@@ -777,16 +777,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I7" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J7" s="1" t="str">
         <v/>
@@ -795,10 +795,10 @@
         <v/>
       </c>
       <c r="L7" s="1">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="M7" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -821,32 +821,32 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="B8" s="1">
-        <v>282</v>
+        <v>2026-05-11</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <v/>
       </c>
       <c r="C8" s="1">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="D8" s="1">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
+        <v>50</v>
+      </c>
+      <c r="G8" s="1">
+        <v>40</v>
+      </c>
+      <c r="H8" s="1">
         <v>30</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>10</v>
       </c>
-      <c r="H8" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I8" s="1" t="str">
-        <v/>
-      </c>
       <c r="J8" s="1" t="str">
         <v/>
       </c>
@@ -854,10 +854,10 @@
         <v/>
       </c>
       <c r="L8" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M8" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N8" s="1" t="str">
         <v>no</v>
@@ -880,43 +880,43 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B9" s="1">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C9" s="1">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="D9" s="1">
+        <v>60</v>
+      </c>
+      <c r="E9" s="1">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1">
         <v>30</v>
-      </c>
-      <c r="E9" s="1">
-        <v>80</v>
-      </c>
-      <c r="F9" s="1">
-        <v>40</v>
       </c>
       <c r="G9" s="1">
         <v>10</v>
       </c>
-      <c r="H9" s="1">
-        <v>60</v>
-      </c>
-      <c r="I9" s="1">
-        <v>20</v>
-      </c>
-      <c r="J9" s="1">
-        <v>20</v>
-      </c>
-      <c r="K9" s="1">
-        <v>10</v>
+      <c r="H9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K9" s="1" t="str">
+        <v/>
       </c>
       <c r="L9" s="1">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M9" s="1">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="N9" s="1" t="str">
         <v>no</v>
@@ -925,7 +925,7 @@
         <v>yes</v>
       </c>
       <c r="P9" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="Q9" s="1" t="str">
         <v>no</v>
@@ -934,48 +934,48 @@
         <v/>
       </c>
       <c r="S9" s="1" t="str">
-        <v>Sugar dip snack</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B10" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C10" s="1">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D10" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1">
+        <v>80</v>
+      </c>
+      <c r="F10" s="1">
+        <v>40</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>60</v>
+      </c>
+      <c r="I10" s="1">
         <v>20</v>
       </c>
-      <c r="F10" s="1">
-        <v>45</v>
-      </c>
-      <c r="G10" s="1">
-        <v>5</v>
-      </c>
-      <c r="H10" s="1">
-        <v>50</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
+        <v>20</v>
+      </c>
+      <c r="K10" s="1">
         <v>10</v>
       </c>
-      <c r="J10" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K10" s="1" t="str">
-        <v/>
-      </c>
       <c r="L10" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M10" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="N10" s="1" t="str">
         <v>no</v>
@@ -984,7 +984,7 @@
         <v>yes</v>
       </c>
       <c r="P10" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q10" s="1" t="str">
         <v>no</v>
@@ -993,37 +993,37 @@
         <v/>
       </c>
       <c r="S10" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B11" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C11" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D11" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G11" s="1">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>50</v>
+      </c>
+      <c r="I11" s="1">
         <v>10</v>
       </c>
-      <c r="H11" s="1">
-        <v>40</v>
-      </c>
-      <c r="I11" s="1">
-        <v>15</v>
-      </c>
       <c r="J11" s="1" t="str">
         <v/>
       </c>
@@ -1031,10 +1031,10 @@
         <v/>
       </c>
       <c r="L11" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M11" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N11" s="1" t="str">
         <v>no</v>
@@ -1057,43 +1057,43 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B12" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C12" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D12" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1">
+        <v>11</v>
+      </c>
+      <c r="F12" s="1">
         <v>0</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
         <v>40</v>
       </c>
-      <c r="G12" s="1">
+      <c r="I12" s="1">
         <v>15</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>80</v>
-      </c>
-      <c r="J12" s="1">
-        <v>30</v>
-      </c>
-      <c r="K12" s="1">
-        <v>5</v>
+      <c r="J12" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K12" s="1" t="str">
+        <v/>
       </c>
       <c r="L12" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M12" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N12" s="1" t="str">
         <v>no</v>
@@ -1111,18 +1111,18 @@
         <v/>
       </c>
       <c r="S12" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B13" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C13" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D13" s="1">
         <v>8</v>
@@ -1131,28 +1131,28 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G13" s="1">
         <v>15</v>
       </c>
       <c r="H13" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>15</v>
-      </c>
-      <c r="J13" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K13" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J13" s="1">
+        <v>30</v>
+      </c>
+      <c r="K13" s="1">
+        <v>5</v>
       </c>
       <c r="L13" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M13" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N13" s="1" t="str">
         <v>no</v>
@@ -1170,48 +1170,48 @@
         <v/>
       </c>
       <c r="S13" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B14" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C14" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D14" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G14" s="1">
         <v>15</v>
       </c>
       <c r="H14" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I14" s="1">
-        <v>20</v>
-      </c>
-      <c r="J14" s="1">
-        <v>20</v>
-      </c>
-      <c r="K14" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K14" s="1" t="str">
+        <v/>
       </c>
       <c r="L14" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M14" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N14" s="1" t="str">
         <v>no</v>
@@ -1234,43 +1234,43 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B15" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C15" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D15" s="1">
+        <v>30</v>
+      </c>
+      <c r="E15" s="1">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1">
         <v>40</v>
       </c>
-      <c r="E15" s="1">
-        <v>10</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H15" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I15" s="1">
         <v>20</v>
       </c>
-      <c r="J15" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K15" s="1" t="str">
-        <v/>
+      <c r="J15" s="1">
+        <v>20</v>
+      </c>
+      <c r="K15" s="1">
+        <v>2</v>
       </c>
       <c r="L15" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M15" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N15" s="1" t="str">
         <v>no</v>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B16" s="1">
         <v>287</v>
@@ -1302,57 +1302,116 @@
         <v>198</v>
       </c>
       <c r="D16" s="1">
+        <v>40</v>
+      </c>
+      <c r="E16" s="1">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
         <v>60</v>
       </c>
-      <c r="E16" s="1">
+      <c r="I16" s="1">
+        <v>20</v>
+      </c>
+      <c r="J16" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K16" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L16" s="1">
+        <v>100</v>
+      </c>
+      <c r="M16" s="1">
+        <v>30</v>
+      </c>
+      <c r="N16" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O16" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P16" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q16" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R16" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S16" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B17" s="1">
+        <v>287</v>
+      </c>
+      <c r="C17" s="1">
+        <v>198</v>
+      </c>
+      <c r="D17" s="1">
+        <v>60</v>
+      </c>
+      <c r="E17" s="1">
         <v>15</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F17" s="1">
         <v>60</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G17" s="1">
         <v>10</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H17" s="1">
         <v>40</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I17" s="1">
         <v>10</v>
       </c>
-      <c r="J16" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K16" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L16" s="1">
+      <c r="J17" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K17" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L17" s="1">
         <v>160</v>
       </c>
-      <c r="M16" s="1">
+      <c r="M17" s="1">
         <v>35</v>
       </c>
-      <c r="N16" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="O16" s="1" t="str">
-        <v>yes</v>
-      </c>
-      <c r="P16" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="Q16" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="R16" s="1" t="str">
-        <v/>
-      </c>
-      <c r="S16" s="1" t="str">
+      <c r="N17" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O17" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P17" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q17" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R17" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S17" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,22 +467,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="B2" s="1">
         <v>283</v>
       </c>
       <c r="C2" s="1">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="D2" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
@@ -500,7 +500,7 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M2" s="1">
         <v>10</v>
@@ -509,7 +509,7 @@
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>
@@ -526,31 +526,31 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="B3" s="1">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C3" s="1">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1">
-        <v>80</v>
-      </c>
-      <c r="I3" s="1">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I3" s="1" t="str">
+        <v/>
       </c>
       <c r="J3" s="1" t="str">
         <v/>
@@ -559,16 +559,16 @@
         <v/>
       </c>
       <c r="L3" s="1">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="M3" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N3" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="O3" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P3" s="1" t="str">
         <v>no</v>
@@ -585,31 +585,31 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="B4" s="1">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C4" s="1">
-        <v>213</v>
-      </c>
-      <c r="D4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="H4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I4" s="1" t="str">
-        <v/>
+        <v>277</v>
+      </c>
+      <c r="D4" s="1">
+        <v>60</v>
+      </c>
+      <c r="E4" s="1">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>80</v>
+      </c>
+      <c r="I4" s="1">
+        <v>5</v>
       </c>
       <c r="J4" s="1" t="str">
         <v/>
@@ -618,10 +618,10 @@
         <v/>
       </c>
       <c r="L4" s="1">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M4" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>yes</v>
@@ -644,25 +644,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-15</v>
       </c>
       <c r="B5" s="1">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C5" s="1">
-        <v>242</v>
-      </c>
-      <c r="D5" s="1">
-        <v>40</v>
-      </c>
-      <c r="E5" s="1">
-        <v>5</v>
-      </c>
-      <c r="F5" s="1">
-        <v>60</v>
-      </c>
-      <c r="G5" s="1">
-        <v>5</v>
+        <v>213</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G5" s="1" t="str">
+        <v/>
       </c>
       <c r="H5" s="1" t="str">
         <v/>
@@ -677,13 +677,13 @@
         <v/>
       </c>
       <c r="L5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N5" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="O5" s="1" t="str">
         <v>yes</v>
@@ -703,43 +703,43 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B6" s="1">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C6" s="1">
-        <v>144</v>
+        <v>242</v>
       </c>
       <c r="D6" s="1">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
-      <c r="H6" s="1">
-        <v>60</v>
-      </c>
-      <c r="I6" s="1">
-        <v>10</v>
-      </c>
-      <c r="J6" s="1">
-        <v>60</v>
-      </c>
-      <c r="K6" s="1">
-        <v>10</v>
+      <c r="H6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K6" s="1" t="str">
+        <v/>
       </c>
       <c r="L6" s="1">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="M6" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="N6" s="1" t="str">
         <v>no</v>
@@ -762,13 +762,13 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="B7" s="1">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C7" s="1">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D7" s="1">
         <v>15</v>
@@ -777,25 +777,25 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7" s="1">
         <v>60</v>
       </c>
       <c r="I7" s="1">
-        <v>15</v>
-      </c>
-      <c r="J7" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K7" s="1" t="str">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="J7" s="1">
+        <v>60</v>
+      </c>
+      <c r="K7" s="1">
+        <v>10</v>
       </c>
       <c r="L7" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="M7" s="1">
         <v>25</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="B8" s="1" t="str">
-        <v/>
+        <v>2026-05-12</v>
+      </c>
+      <c r="B8" s="1">
+        <v>286</v>
       </c>
       <c r="C8" s="1">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="D8" s="1">
         <v>15</v>
@@ -836,16 +836,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G8" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H8" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I8" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J8" s="1" t="str">
         <v/>
@@ -854,10 +854,10 @@
         <v/>
       </c>
       <c r="L8" s="1">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="M8" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N8" s="1" t="str">
         <v>no</v>
@@ -880,31 +880,31 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="B9" s="1">
-        <v>282</v>
+        <v>2026-05-11</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <v/>
       </c>
       <c r="C9" s="1">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="D9" s="1">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
+        <v>50</v>
+      </c>
+      <c r="G9" s="1">
+        <v>40</v>
+      </c>
+      <c r="H9" s="1">
         <v>30</v>
       </c>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I9" s="1" t="str">
-        <v/>
+      <c r="I9" s="1">
+        <v>10</v>
       </c>
       <c r="J9" s="1" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v/>
       </c>
       <c r="L9" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M9" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N9" s="1" t="str">
         <v>no</v>
@@ -939,43 +939,43 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B10" s="1">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C10" s="1">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="D10" s="1">
+        <v>60</v>
+      </c>
+      <c r="E10" s="1">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1">
         <v>30</v>
       </c>
-      <c r="E10" s="1">
-        <v>80</v>
-      </c>
-      <c r="F10" s="1">
-        <v>40</v>
-      </c>
       <c r="G10" s="1">
         <v>10</v>
       </c>
-      <c r="H10" s="1">
-        <v>60</v>
-      </c>
-      <c r="I10" s="1">
-        <v>20</v>
-      </c>
-      <c r="J10" s="1">
-        <v>20</v>
-      </c>
-      <c r="K10" s="1">
-        <v>10</v>
+      <c r="H10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K10" s="1" t="str">
+        <v/>
       </c>
       <c r="L10" s="1">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M10" s="1">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="N10" s="1" t="str">
         <v>no</v>
@@ -984,7 +984,7 @@
         <v>yes</v>
       </c>
       <c r="P10" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="Q10" s="1" t="str">
         <v>no</v>
@@ -993,48 +993,48 @@
         <v/>
       </c>
       <c r="S10" s="1" t="str">
-        <v>Sugar dip snack</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B11" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C11" s="1">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D11" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1">
+        <v>80</v>
+      </c>
+      <c r="F11" s="1">
+        <v>40</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>60</v>
+      </c>
+      <c r="I11" s="1">
         <v>20</v>
       </c>
-      <c r="F11" s="1">
-        <v>45</v>
-      </c>
-      <c r="G11" s="1">
-        <v>5</v>
-      </c>
-      <c r="H11" s="1">
-        <v>50</v>
-      </c>
-      <c r="I11" s="1">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K11" s="1" t="str">
-        <v/>
+      <c r="J11" s="1">
+        <v>20</v>
+      </c>
+      <c r="K11" s="1">
+        <v>10</v>
       </c>
       <c r="L11" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M11" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="N11" s="1" t="str">
         <v>no</v>
@@ -1043,7 +1043,7 @@
         <v>yes</v>
       </c>
       <c r="P11" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q11" s="1" t="str">
         <v>no</v>
@@ -1052,36 +1052,36 @@
         <v/>
       </c>
       <c r="S11" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B12" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C12" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D12" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G12" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H12" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I12" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J12" s="1" t="str">
         <v/>
@@ -1090,10 +1090,10 @@
         <v/>
       </c>
       <c r="L12" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M12" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N12" s="1" t="str">
         <v>no</v>
@@ -1116,43 +1116,43 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B13" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C13" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D13" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1">
         <v>40</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>15</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>80</v>
-      </c>
-      <c r="J13" s="1">
-        <v>30</v>
-      </c>
-      <c r="K13" s="1">
-        <v>5</v>
+      <c r="J13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K13" s="1" t="str">
+        <v/>
       </c>
       <c r="L13" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M13" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N13" s="1" t="str">
         <v>no</v>
@@ -1170,18 +1170,18 @@
         <v/>
       </c>
       <c r="S13" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B14" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C14" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D14" s="1">
         <v>8</v>
@@ -1190,28 +1190,28 @@
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G14" s="1">
         <v>15</v>
       </c>
       <c r="H14" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1">
-        <v>15</v>
-      </c>
-      <c r="J14" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K14" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J14" s="1">
+        <v>30</v>
+      </c>
+      <c r="K14" s="1">
+        <v>5</v>
       </c>
       <c r="L14" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M14" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N14" s="1" t="str">
         <v>no</v>
@@ -1229,48 +1229,48 @@
         <v/>
       </c>
       <c r="S14" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B15" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C15" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D15" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G15" s="1">
         <v>15</v>
       </c>
       <c r="H15" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I15" s="1">
-        <v>20</v>
-      </c>
-      <c r="J15" s="1">
-        <v>20</v>
-      </c>
-      <c r="K15" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J15" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K15" s="1" t="str">
+        <v/>
       </c>
       <c r="L15" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M15" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N15" s="1" t="str">
         <v>no</v>
@@ -1293,43 +1293,43 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B16" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C16" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D16" s="1">
+        <v>30</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5</v>
+      </c>
+      <c r="F16" s="1">
         <v>40</v>
       </c>
-      <c r="E16" s="1">
-        <v>10</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H16" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I16" s="1">
         <v>20</v>
       </c>
-      <c r="J16" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K16" s="1" t="str">
-        <v/>
+      <c r="J16" s="1">
+        <v>20</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2</v>
       </c>
       <c r="L16" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M16" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N16" s="1" t="str">
         <v>no</v>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B17" s="1">
         <v>287</v>
@@ -1361,57 +1361,116 @@
         <v>198</v>
       </c>
       <c r="D17" s="1">
+        <v>40</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
         <v>60</v>
       </c>
-      <c r="E17" s="1">
+      <c r="I17" s="1">
+        <v>20</v>
+      </c>
+      <c r="J17" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K17" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L17" s="1">
+        <v>100</v>
+      </c>
+      <c r="M17" s="1">
+        <v>30</v>
+      </c>
+      <c r="N17" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O17" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P17" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q17" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R17" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S17" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B18" s="1">
+        <v>287</v>
+      </c>
+      <c r="C18" s="1">
+        <v>198</v>
+      </c>
+      <c r="D18" s="1">
+        <v>60</v>
+      </c>
+      <c r="E18" s="1">
         <v>15</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F18" s="1">
         <v>60</v>
       </c>
-      <c r="G17" s="1">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
         <v>40</v>
       </c>
-      <c r="I17" s="1">
-        <v>10</v>
-      </c>
-      <c r="J17" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K17" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L17" s="1">
+      <c r="I18" s="1">
+        <v>10</v>
+      </c>
+      <c r="J18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L18" s="1">
         <v>160</v>
       </c>
-      <c r="M17" s="1">
+      <c r="M18" s="1">
         <v>35</v>
       </c>
-      <c r="N17" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="O17" s="1" t="str">
-        <v>yes</v>
-      </c>
-      <c r="P17" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="Q17" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="R17" s="1" t="str">
-        <v/>
-      </c>
-      <c r="S17" s="1" t="str">
+      <c r="N18" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O18" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P18" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q18" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S18" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -467,25 +467,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="B2" s="1">
         <v>283</v>
       </c>
       <c r="C2" s="1">
-        <v>272</v>
-      </c>
-      <c r="D2" s="1">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
-        <v>60</v>
-      </c>
-      <c r="G2" s="1">
-        <v>10</v>
+        <v>350</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v/>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>
@@ -526,22 +526,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="B3" s="1">
         <v>283</v>
       </c>
       <c r="C3" s="1">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G3" s="1">
         <v>10</v>
@@ -559,7 +559,7 @@
         <v/>
       </c>
       <c r="L3" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M3" s="1">
         <v>10</v>
@@ -568,7 +568,7 @@
         <v>no</v>
       </c>
       <c r="O3" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P3" s="1" t="str">
         <v>no</v>
@@ -585,31 +585,31 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="B4" s="1">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C4" s="1">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="D4" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>80</v>
-      </c>
-      <c r="I4" s="1">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I4" s="1" t="str">
+        <v/>
       </c>
       <c r="J4" s="1" t="str">
         <v/>
@@ -618,16 +618,16 @@
         <v/>
       </c>
       <c r="L4" s="1">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="M4" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N4" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="O4" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="P4" s="1" t="str">
         <v>no</v>
@@ -644,31 +644,31 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="B5" s="1">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C5" s="1">
-        <v>213</v>
-      </c>
-      <c r="D5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="H5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="1" t="str">
-        <v/>
+        <v>277</v>
+      </c>
+      <c r="D5" s="1">
+        <v>60</v>
+      </c>
+      <c r="E5" s="1">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>80</v>
+      </c>
+      <c r="I5" s="1">
+        <v>5</v>
       </c>
       <c r="J5" s="1" t="str">
         <v/>
@@ -677,10 +677,10 @@
         <v/>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M5" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N5" s="1" t="str">
         <v>yes</v>
@@ -703,25 +703,25 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-15</v>
       </c>
       <c r="B6" s="1">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C6" s="1">
-        <v>242</v>
-      </c>
-      <c r="D6" s="1">
-        <v>40</v>
-      </c>
-      <c r="E6" s="1">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1">
-        <v>60</v>
-      </c>
-      <c r="G6" s="1">
-        <v>5</v>
+        <v>213</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="E6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="F6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="G6" s="1" t="str">
+        <v/>
       </c>
       <c r="H6" s="1" t="str">
         <v/>
@@ -736,13 +736,13 @@
         <v/>
       </c>
       <c r="L6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N6" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="O6" s="1" t="str">
         <v>yes</v>
@@ -762,43 +762,43 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B7" s="1">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C7" s="1">
-        <v>144</v>
+        <v>242</v>
       </c>
       <c r="D7" s="1">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
       </c>
-      <c r="H7" s="1">
-        <v>60</v>
-      </c>
-      <c r="I7" s="1">
-        <v>10</v>
-      </c>
-      <c r="J7" s="1">
-        <v>60</v>
-      </c>
-      <c r="K7" s="1">
-        <v>10</v>
+      <c r="H7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J7" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K7" s="1" t="str">
+        <v/>
       </c>
       <c r="L7" s="1">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="M7" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="N7" s="1" t="str">
         <v>no</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="B8" s="1">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C8" s="1">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D8" s="1">
         <v>15</v>
@@ -836,25 +836,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H8" s="1">
         <v>60</v>
       </c>
       <c r="I8" s="1">
-        <v>15</v>
-      </c>
-      <c r="J8" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K8" s="1" t="str">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="J8" s="1">
+        <v>60</v>
+      </c>
+      <c r="K8" s="1">
+        <v>10</v>
       </c>
       <c r="L8" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="M8" s="1">
         <v>25</v>
@@ -880,13 +880,13 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="B9" s="1" t="str">
-        <v/>
+        <v>2026-05-12</v>
+      </c>
+      <c r="B9" s="1">
+        <v>286</v>
       </c>
       <c r="C9" s="1">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="D9" s="1">
         <v>15</v>
@@ -895,16 +895,16 @@
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G9" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H9" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I9" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J9" s="1" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v/>
       </c>
       <c r="L9" s="1">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="M9" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N9" s="1" t="str">
         <v>no</v>
@@ -939,31 +939,31 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="B10" s="1">
-        <v>282</v>
+        <v>2026-05-11</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <v/>
       </c>
       <c r="C10" s="1">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="D10" s="1">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1">
+        <v>40</v>
+      </c>
+      <c r="H10" s="1">
         <v>30</v>
       </c>
-      <c r="G10" s="1">
-        <v>10</v>
-      </c>
-      <c r="H10" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I10" s="1" t="str">
-        <v/>
+      <c r="I10" s="1">
+        <v>10</v>
       </c>
       <c r="J10" s="1" t="str">
         <v/>
@@ -972,10 +972,10 @@
         <v/>
       </c>
       <c r="L10" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M10" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N10" s="1" t="str">
         <v>no</v>
@@ -998,43 +998,43 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B11" s="1">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C11" s="1">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="D11" s="1">
+        <v>60</v>
+      </c>
+      <c r="E11" s="1">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1">
         <v>30</v>
       </c>
-      <c r="E11" s="1">
-        <v>80</v>
-      </c>
-      <c r="F11" s="1">
-        <v>40</v>
-      </c>
       <c r="G11" s="1">
         <v>10</v>
       </c>
-      <c r="H11" s="1">
-        <v>60</v>
-      </c>
-      <c r="I11" s="1">
-        <v>20</v>
-      </c>
-      <c r="J11" s="1">
-        <v>20</v>
-      </c>
-      <c r="K11" s="1">
-        <v>10</v>
+      <c r="H11" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I11" s="1" t="str">
+        <v/>
+      </c>
+      <c r="J11" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K11" s="1" t="str">
+        <v/>
       </c>
       <c r="L11" s="1">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M11" s="1">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="N11" s="1" t="str">
         <v>no</v>
@@ -1043,7 +1043,7 @@
         <v>yes</v>
       </c>
       <c r="P11" s="1" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="Q11" s="1" t="str">
         <v>no</v>
@@ -1052,48 +1052,48 @@
         <v/>
       </c>
       <c r="S11" s="1" t="str">
-        <v>Sugar dip snack</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B12" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C12" s="1">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="D12" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1">
+        <v>80</v>
+      </c>
+      <c r="F12" s="1">
+        <v>40</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>60</v>
+      </c>
+      <c r="I12" s="1">
         <v>20</v>
       </c>
-      <c r="F12" s="1">
-        <v>45</v>
-      </c>
-      <c r="G12" s="1">
-        <v>5</v>
-      </c>
-      <c r="H12" s="1">
-        <v>50</v>
-      </c>
-      <c r="I12" s="1">
-        <v>10</v>
-      </c>
-      <c r="J12" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K12" s="1" t="str">
-        <v/>
+      <c r="J12" s="1">
+        <v>20</v>
+      </c>
+      <c r="K12" s="1">
+        <v>10</v>
       </c>
       <c r="L12" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="M12" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="N12" s="1" t="str">
         <v>no</v>
@@ -1102,7 +1102,7 @@
         <v>yes</v>
       </c>
       <c r="P12" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q12" s="1" t="str">
         <v>no</v>
@@ -1111,36 +1111,36 @@
         <v/>
       </c>
       <c r="S12" s="1" t="str">
-        <v/>
+        <v>Sugar dip snack</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B13" s="1">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C13" s="1">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D13" s="1">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G13" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H13" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I13" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J13" s="1" t="str">
         <v/>
@@ -1149,10 +1149,10 @@
         <v/>
       </c>
       <c r="L13" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M13" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N13" s="1" t="str">
         <v>no</v>
@@ -1175,43 +1175,43 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B14" s="1">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C14" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="D14" s="1">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1">
         <v>40</v>
       </c>
-      <c r="G14" s="1">
+      <c r="I14" s="1">
         <v>15</v>
       </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>80</v>
-      </c>
-      <c r="J14" s="1">
-        <v>30</v>
-      </c>
-      <c r="K14" s="1">
-        <v>5</v>
+      <c r="J14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K14" s="1" t="str">
+        <v/>
       </c>
       <c r="L14" s="1">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="M14" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="N14" s="1" t="str">
         <v>no</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="S14" s="1" t="str">
-        <v>1lb of ground turkey is 80g protein</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B15" s="1">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C15" s="1">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D15" s="1">
         <v>8</v>
@@ -1249,28 +1249,28 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G15" s="1">
         <v>15</v>
       </c>
       <c r="H15" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>15</v>
-      </c>
-      <c r="J15" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K15" s="1" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="J15" s="1">
+        <v>30</v>
+      </c>
+      <c r="K15" s="1">
+        <v>5</v>
       </c>
       <c r="L15" s="1">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="M15" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N15" s="1" t="str">
         <v>no</v>
@@ -1288,48 +1288,48 @@
         <v/>
       </c>
       <c r="S15" s="1" t="str">
-        <v/>
+        <v>1lb of ground turkey is 80g protein</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="B16" s="1">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C16" s="1">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="D16" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
       <c r="H16" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I16" s="1">
-        <v>20</v>
-      </c>
-      <c r="J16" s="1">
-        <v>20</v>
-      </c>
-      <c r="K16" s="1">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="J16" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K16" s="1" t="str">
+        <v/>
       </c>
       <c r="L16" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M16" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N16" s="1" t="str">
         <v>no</v>
@@ -1352,43 +1352,43 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="B17" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C17" s="1">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D17" s="1">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5</v>
+      </c>
+      <c r="F17" s="1">
         <v>40</v>
       </c>
-      <c r="E17" s="1">
-        <v>10</v>
-      </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H17" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I17" s="1">
         <v>20</v>
       </c>
-      <c r="J17" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K17" s="1" t="str">
-        <v/>
+      <c r="J17" s="1">
+        <v>20</v>
+      </c>
+      <c r="K17" s="1">
+        <v>2</v>
       </c>
       <c r="L17" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M17" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N17" s="1" t="str">
         <v>no</v>
@@ -1411,7 +1411,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="B18" s="1">
         <v>287</v>
@@ -1420,57 +1420,116 @@
         <v>198</v>
       </c>
       <c r="D18" s="1">
+        <v>40</v>
+      </c>
+      <c r="E18" s="1">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
         <v>60</v>
       </c>
-      <c r="E18" s="1">
+      <c r="I18" s="1">
+        <v>20</v>
+      </c>
+      <c r="J18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L18" s="1">
+        <v>100</v>
+      </c>
+      <c r="M18" s="1">
+        <v>30</v>
+      </c>
+      <c r="N18" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O18" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P18" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q18" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R18" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S18" s="1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="B19" s="1">
+        <v>287</v>
+      </c>
+      <c r="C19" s="1">
+        <v>198</v>
+      </c>
+      <c r="D19" s="1">
+        <v>60</v>
+      </c>
+      <c r="E19" s="1">
         <v>15</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F19" s="1">
         <v>60</v>
       </c>
-      <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
         <v>40</v>
       </c>
-      <c r="I18" s="1">
-        <v>10</v>
-      </c>
-      <c r="J18" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K18" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L18" s="1">
+      <c r="I19" s="1">
+        <v>10</v>
+      </c>
+      <c r="J19" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K19" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L19" s="1">
         <v>160</v>
       </c>
-      <c r="M18" s="1">
+      <c r="M19" s="1">
         <v>35</v>
       </c>
-      <c r="N18" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="O18" s="1" t="str">
-        <v>yes</v>
-      </c>
-      <c r="P18" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="Q18" s="1" t="str">
-        <v>no</v>
-      </c>
-      <c r="R18" s="1" t="str">
-        <v/>
-      </c>
-      <c r="S18" s="1" t="str">
+      <c r="N19" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="O19" s="1" t="str">
+        <v>yes</v>
+      </c>
+      <c r="P19" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q19" s="1" t="str">
+        <v>no</v>
+      </c>
+      <c r="R19" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S19" s="1" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -475,17 +475,17 @@
       <c r="C2" s="1">
         <v>350</v>
       </c>
-      <c r="D2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
-        <v/>
+      <c r="D2" s="1">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5</v>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
@@ -500,16 +500,16 @@
         <v/>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O2" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P2" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -546,23 +546,23 @@
       <c r="G3" s="1">
         <v>10</v>
       </c>
-      <c r="H3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="J3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K3" s="1" t="str">
-        <v/>
+      <c r="H3" s="1">
+        <v>60</v>
+      </c>
+      <c r="I3" s="1">
+        <v>10</v>
+      </c>
+      <c r="J3" s="1">
+        <v>60</v>
+      </c>
+      <c r="K3" s="1">
+        <v>5</v>
       </c>
       <c r="L3" s="1">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="M3" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="N3" s="1" t="str">
         <v>no</v>
@@ -571,7 +571,7 @@
         <v>yes</v>
       </c>
       <c r="P3" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="Q3" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -605,11 +605,11 @@
       <c r="G4" s="1">
         <v>10</v>
       </c>
-      <c r="H4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I4" s="1" t="str">
-        <v/>
+      <c r="H4" s="1">
+        <v>40</v>
+      </c>
+      <c r="I4" s="1">
+        <v>20</v>
       </c>
       <c r="J4" s="1" t="str">
         <v/>
@@ -618,16 +618,16 @@
         <v/>
       </c>
       <c r="L4" s="1">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="M4" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N4" s="1" t="str">
         <v>no</v>
       </c>
       <c r="O4" s="1" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="P4" s="1" t="str">
         <v>no</v>

--- a/Health_Tracker.xlsx
+++ b/Health_Tracker.xlsx
@@ -487,11 +487,11 @@
       <c r="G2" s="1">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1" t="str">
-        <v/>
+      <c r="H2" s="1">
+        <v>5</v>
+      </c>
+      <c r="I2" s="1">
+        <v>30</v>
       </c>
       <c r="J2" s="1" t="str">
         <v/>
@@ -500,10 +500,10 @@
         <v/>
       </c>
       <c r="L2" s="1">
+        <v>40</v>
+      </c>
+      <c r="M2" s="1">
         <v>35</v>
-      </c>
-      <c r="M2" s="1">
-        <v>5</v>
       </c>
       <c r="N2" s="1" t="str">
         <v>no</v>
